--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/employee_timeline.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/employee_timeline.xlsx
@@ -55,7 +55,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -82,7 +82,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/10001_09-2024_Brutto_NettoProbe_00107_QZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00107_QZ1.pdf</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -94,7 +94,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2021-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -104,12 +104,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
+          <t>ADAC, Hansastr; MP, MARTIN ZAHARIEVSOZIALVERSICHER; Rundfunk ARD, ZDF; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/12-2024_Brutto_Netto_00090_X0B.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -121,22 +121,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avis Budget Autovermietung Verwaltungsgesellschaft mbH, Oberursel; KG, Amtsgericht Bad Homburg v; OBERURSEL, GERMANY; Sollten Sie Fragen, Wünsche oder auch Beanstandungen haben; Wir hoffen, Sie bald wieder bei uns begrüssen zu dürfen; ZAHARIEV,MARTIN; ZAHARIEV,MARTIN Gefahrene Entfernung</t>
+          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; Burger King, FOOD STAR GmbH; GLOBUS SBW, CHEMNITZ; Globus SBW, Chemnitz; Gutschrift Darling züruck , Danke Mersi; MP, INH; MP, MARTIN ZAHARIEVSOZIALVERSICHER; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/307538032.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -148,76 +148,76 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t/>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t/>
+          <t>9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t/>
+          <t>ADAC Versicherung AG, Hansastr; ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; Burger King, FOOD STAR GmbH; EUR, SOL; KG, Ihr Einkauf bei Parf; MP, INH; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/38389 - Vorgangsmappe Lohn - Aktualisiert- Auszahlungen Inflationsprämie.xlsx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2023 #9109.pdf</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t/>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t/>
+          <t>ADAC, Hansastr; MP, MARTIN ZAHARIEVSOZIALVERSICHER; Rundfunk ARD, ZDF; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; BUONO, CHEMNITZ; GLOBUS SBW, CHEMNITZ; Gutschrift Darling züruck , Danke Mersi; MP, INH; Reece Upadhyay, Ihr Einkauf bei R; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -229,22 +229,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Auftrag unseres Mandanten, Martin Zahariev; Brunettin, Marilie</t>
+          <t>ADAC, Hansastr; ARD, ZDF; DANKE, IHR LIDL; MP, MARTIN ZAHARIEVSOZIALVERSICHER; Simply NetTrade GmbH, Ihr Einkauf bei Simply NetTrade Gmb; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/89878877, Antrag auf Ratenzahlung.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -256,22 +256,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brunettin, Marco; Kind regards, Marco; Marco Brunettin, LL</t>
+          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTO CENTER SUED, CHEMNITZ; BRAZIL OHG, CHEMNITZ; BUONO, CHEMNITZ; MP, INH; Reece Upadhyay, Ihr Einkauf bei R; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 01-2025.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -283,22 +283,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brunettin, Marco; Kind regards, Marco; Marco Brunettin, LL</t>
+          <t>ADAC, Hansastr; ARD, ZDF; Burger King, FOOD STAR GmbH; DANKE, IHR LIDL; MP, MARTIN ZAHARIEVSOZIALVERSICHER; Simply NetTrade GmbH, Ihr Einkauf bei Simply NetTrade Gmb; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -310,22 +310,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brunettin, Marco; Kind regards, Marco; Marco Brunettin, LL</t>
+          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTO CENTER SUED, CHEMNITZ; MP, INH; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2025.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -337,22 +337,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brunettin, Marco; Kind regards, Marco; Marco Brunettin, LL</t>
+          <t>ADAC, Hansastr; ARD, ZDF; BRAZIL OHG, CHEMNITZ; Burger King, FOOD STAR GmbH; DANKE, IHR LIDL; MP, MARTIN ZAHARIEVSOZIALVERSICHER; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 03-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/09-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -364,22 +364,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brunettin, Marco; Kind regards, Marco; Marco Brunettin, LL</t>
+          <t>ADAC, Hansastr; AGIP,ANSBACHER STR; AGIP,NUERNBERG; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTO CENTER SUED, CHEMNITZ; BUONO, CHEMNITZ; Burger King, FOOD STAR GmbH; MP, INH; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 04-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/10-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -391,22 +391,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brunettin, Marco; Kind regards, Marco; Marco Brunettin, LL</t>
+          <t>ADAC, Hansastr; ARD, ZDF; FAVORIT MP, MARTINSOZIALVERSICHERU; MP, MARTIN ZAHARIEVSOZIALVERSICHER; MP, MARTIN ZAHARIEVSOZIALVERSICHERU; ZAHARIEV, MARTIN ADAC VERSICHER; Überweisung Kirev,Kosta</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 05-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/11-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -418,22 +418,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brunettin, Marco; Marco Brunettin, LL</t>
+          <t>ADAC, Hansastr; ARD, ZDF; Burger King, FOOD STAR GmbH; EUR, UMS; FAVORIT MP, MARTINSOZIALVERSICHERU; GLOBUS SBW, CHEMNITZ; Globus SBW, Chemnitz; MP, MARTIN ZAHARIEVSOZIALVERSICHER; MP, MARTIN ZAHARIEVSOZIALVERSICHERU; ZAHARIEV, MARTIN ADAC VERSICHER; Überweisung Kirev,Kosta</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 06-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -445,22 +445,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brunettin, Marco; Kind regards, Marco; Marco Brunettin, LL</t>
+          <t>ADAC, Hansastr; AGIP,ANSBACHER STR; AGIP,NUERNBERG; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTO CENTER SUED, CHEMNITZ; BUONO, CHEMNITZ; Burger King, FOOD STAR GmbH; KG, Ihr Einkauf bei Parf; MP, INH; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 07-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -472,22 +472,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brunettin, Marco; Kind regards, Marco; Marco Brunettin, LL</t>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 09-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2024_Brutto_Netto_00090_X0B.pdf</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -499,49 +499,49 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brunettin, Marco; Marco Brunettin, LL</t>
+          <t/>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 10-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brunettin, Marco; Kind regards, Marco; Marco Brunettin, LL</t>
+          <t>Betreuung durch den ASD, Bescheid; EUR Warenlieferung, Forderung aus; Feuerwehr Zwickau, Kennzeichen; Ieva Meilutyte, Stefan Mihaila; Säumniszuschläge, Kosten; Säumniszuschläge, Nachzahlungszinsen und; Säumniszuschläge, Zinsen; Ventsislav Kostov, Ionel Neamtu; ZV-Sache, AG Chemnitz; Zahariev, Martin</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 11-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -558,17 +558,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brunettin, Marco; Kind regards, Marco; Marco Brunettin, LL</t>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 12-2024.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Vasilev_Test Pay Slip.pdf</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -580,103 +580,103 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t/>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t/>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brunettin, Marco; Brunettin, Marilie; Hello again, I called the AOK Plus</t>
+          <t/>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Aok plus.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/38389 - Vorgangsmappe Lohn - 38389 - Aktualisiert- Auszahlungen Inflationsprämie.xlsx</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t/>
+          <t>2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t/>
+          <t>Marco Brunettin; Marco Brunettin, LL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/CarlundCarla_RG424005125.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t/>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t/>
+          <t>14</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t/>
+          <t>Boulevard Royal, L; Der Verkäufer behält sich vor, Verarbeitungsaufträge abzulehnen; E-Mail, Fax oder Brief; EE Amsterdam, Niederlande; Grafiken in den vom Verkäufer vorgegebenen Dateiformaten, Formatierungen; Kennedy, L; Reklamationen, Widerrufserklärungen und; Reklamationen, Widerrufserklärungen und -zusendungen oder Gutschriften; Stockholm, Schweden; Urheber-, Marken- und Persönlichkeitsrechte; Versendung, Retouren; Ware, Lieferzeit; Zahlungsabwicklung über die TeamBank AG Nürnberg, Beuthener Straße; Überweisungsgebühren, Wechselkursgebühren</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/CarlundCarla_RG424005157.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/agb_doc.pdf</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brunettin, Marilie; Hello again, I have spoken to the DAK</t>
+          <t>Autoverwertung-Oskar, Schulstr</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/DAK.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Rechnung_RE058675_11.08.2025.pdf</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -688,22 +688,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t/>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißlog, Hohensteiner Str</t>
+          <t>Herleshausen, Deutschland; Post versandter Brief, Telefax oder E-Mail; Weber GmbH, Sülzbach</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Docutain Dokument.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/widerruf_doc.pdf</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -715,22 +715,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Goetz, Schneeberg; Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t>Parfumerie Douglas GmbH, Ihr Eink auf bei Parfumeri; Parfumerie Douglas GmbH, Ihr Einkau; Skull Sh aver EU Ltd, Ihr Ei; Skull Shaver EU Ltd, Ihr Einkauf bei Skull Shaver EU Lt</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Gutschrift 34-2024 Zahariev Martin 04.10.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/01-2023 #9120.pdf</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -742,22 +742,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t>ALEX Chemnitz, Galerie Roter Turm; Burger King, FOOD STAR GmbH; Limited, Ih</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/gutschrift 71 2025 zahariev Sendungsverlust.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/02-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -769,22 +769,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brunettin, Marilie</t>
+          <t>ALEX Chemnitz, Galerie Roter Turm; AUTODOC AG, Ihr Einkau; Burger King, FOOD STAR GmbH; Dott, Ihr Einkauf bei Dott; EUR, Tra; Limited, Ih; Tier Mobility GmbH, Ihr Einkauf b</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Health insurance fund reimbursements.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/04-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -796,22 +796,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brunettin, Marilie</t>
+          <t>ALEX Chemnitz, Galerie Roter Turm; AUTO CENTER SUED, CHEMNITZ; AUTODOC AG, Ihr Einkau; Dott, Ihr Einkauf bei Dott; Tier Mobility GmbH, Ihr Einkauf b</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Ihre Lohnauswertungen.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/06-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -823,22 +823,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Timothy Grygotis, Julia von SpechtSitz</t>
+          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KD-Nr. 550980 - Pre-Not._Nr. 6102600491.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/07-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -850,22 +850,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Timothy Grygotis, Julia von SpechtSitz</t>
+          <t>ADAC, Hansastr; AG, Ihr Einkauf bei AUTODOC AG; ALEX Chemnitz, Galerie Roter Turm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KD-Nr. 550980 - Pre-Not._Nr. 6102659867.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -877,22 +877,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Timothy Grygotis, Julia von SpechtSitz</t>
+          <t>AG, Ihr Einkauf bei AUTODOC AG; EU Ltd, Ihr Einkauf bei Skull; GmbH, Ihr Einkauf bei Parfumerie Do; Parfumerie Douglas GmbH, Ihr Eink</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KD-Nr. 550980 - Pre-Not._Nr. 6102665850.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/12-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -904,22 +904,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Timothy Grygotis, Julia von SpechtSitz</t>
+          <t>Akkreditiert durch DAkkS, Registriernummer; Berlin-Charlottenburg, HRB; Präqualifikation Kurier-, Express- und Paketdienstleistern i; ZERTIFIZIERUNG BAU GMBH, Kronenstraße</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KD-Nr. 550980 - Pre-Not._Nr. 6102698674.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/20240123_60222_10160_Rechnung.pdf</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -931,22 +931,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brunettin, Marilie; Good morning Martin, I have just called the KKH</t>
+          <t>Timothy Grygotis, Julia von SpechtSitz</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KKH1.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102600491.PDF</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brunettin, Marilie</t>
+          <t>Timothy Grygotis, Julia von SpechtSitz</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Mahnbescheid Amtsgericht Euskirchen _ AXA.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102659867.PDF</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -985,22 +985,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t>Timothy Grygotis, Julia von SpechtSitz</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Martin Zahariev Gutschrift 51 17.02.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102665850.PDF</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1012,22 +1012,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t>Timothy Grygotis, Julia von SpechtSitz</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Martin Zahariev Gutschrift 55 08.03.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102698674.PDF</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2058-08</t>
+          <t/>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>Andreas Weber, Horst WeberHandelsregister</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Martin Zahariev Transporte 2058 08.03.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073-1.pdf</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1066,22 +1066,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t/>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brunettin, Marilie; Good morning Martin, I have just called the KKH; When it is paid, I can ask for the Unbedenklichkeitsbescheingungen</t>
+          <t>Andreas Weber, Horst WeberHandelsregister</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/original_msg(2).eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073.pdf</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1093,7 +1093,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brunettin, Marilie</t>
+          <t>Timothy Grygotis, Julia von Specht</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Petya Stefanova AOK.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-1.PDF</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1120,22 +1120,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chemnitz , Sachs; Motoren-Frech, Uwe; Thomas Frech GbR, Hohensteiner Straße</t>
+          <t>Timothy Grygotis, Julia von Specht</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/RE-53380_2024 13.08.2024 09_17_16.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-2.PDF</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1147,22 +1147,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chemnitz , Sachs; Motoren-Frech, Uwe; Thomas Frech GbR, Hohensteiner Straße</t>
+          <t>Timothy Grygotis, Julia von Specht</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/RE-53652_2024 20.09.2024 10_56_50.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980.PDF</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1174,22 +1174,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Andreas Weber, Horst WeberHandelsregister</t>
+          <t>Avis Budget Autovermietung Verwaltungsgesellschaft mbH, Oberursel; KG, Amtsgericht Bad Homburg v; OBERURSEL, GERMANY; Sollten Sie Fragen, Wünsche oder auch Beanstandungen haben; Wir hoffen, Sie bald wieder bei uns begrüssen zu dürfen; ZAHARIEV,MARTIN; ZAHARIEV,MARTIN Gefahrene Entfernung</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rechnung RE211073-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/307538032.pdf</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1201,22 +1201,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t/>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Andreas Weber, Horst WeberHandelsregister</t>
+          <t>Marco Brunettin; Marco Brunettin, LL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rechnung RE211073.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/39739 - Rechnung 231128_2023 vom 28.12.2023, Aufträge 31_23, 32_23, 33_23, 34_23, 50_23, 98_23, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1228,22 +1228,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Autoverwertung-Oskar, Schulstr</t>
+          <t>Marco Brunettin; Marco Brunettin, LL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rechnung_RE058675_11.08.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1255,22 +1255,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Timothy Grygotis, Julia von Specht</t>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rücklastschrift _ Ihre KD-Nr. 550980-1.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1282,22 +1282,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Timothy Grygotis, Julia von Specht</t>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rücklastschrift _ Ihre KD-Nr. 550980-2.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1309,22 +1309,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Timothy Grygotis, Julia von Specht</t>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rücklastschrift _ Ihre KD-Nr. 550980.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1336,22 +1336,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Betreuung durch den ASD, Bescheid; EUR Warenlieferung, Forderung aus; Feuerwehr Zwickau, Kennzeichen; Ieva Meilutyte, Stefan Mihaila; Säumniszuschläge, Kosten; Säumniszuschläge, Nachzahlungszinsen und; Säumniszuschläge, Zinsen; Ventsislav Kostov, Ionel Neamtu; ZV-Sache, AG Chemnitz; Zahariev, Martin</t>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1363,22 +1363,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Unternehmerabrechnung - VP 120-2300157425.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1390,22 +1390,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t>Brunettin, Mari; EURPQ, Matodiev wage statement; Marco Brunettin; Marco Brunettin, LL; Stefanova, Yordanov</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Unternehmerabrechnung - VP 120-2300157934.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1417,22 +1417,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Unternehmerabrechnung - VP 120-2400001108-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1444,22 +1444,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Unternehmerabrechnung - VP 120-2400017841.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1471,22 +1471,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Unternehmerabrechnung - VP 120-2400018211.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1498,22 +1498,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Vasilev_Test Pay Slip.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1525,22 +1525,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brunettin, Marilie</t>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Zoll payment.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1552,22 +1552,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t>Arbeitsunfähigkeit, Entgeltbescheinigung bei; Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2024.eml::41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1579,76 +1579,76 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t/>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Arbeitsunfähigkeit, Entgeltbescheinigung bei; Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t/>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2025.eml::46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/CarlundCarla_RG424005125.pdf</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t/>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t/>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 03-2024.eml::41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/CarlundCarla_RG424005157.pdf</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t>Brunettin, Marilie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 04-2024.eml::42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Ihre Lohnauswertungen.eml</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1660,22 +1660,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2036-08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; EURPQ, Matodiev wage statement; Marco Brunettin; Marco Brunettin, LL; Stefanova, Yordanov</t>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 06-2024.eml::43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2036 08.01.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -1687,22 +1687,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2054-07</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 07-2024.eml::43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2054 07.02.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -1714,22 +1714,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2058-08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 09-2024.eml::44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2058 08.03.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -1741,103 +1741,103 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t/>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t/>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 10-2024.eml::45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2765 Zahariev Hermes Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t/>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t/>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 11-2024.eml::45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2777 Zahariev Hermes Unterstützungstouren.pdf</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t/>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t/>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 12-2024.eml::46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2778 Zahariev Hermes Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings012024.zip::40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2782 Zahariev Hermes Bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -1849,115 +1849,115 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Marco Brunettin; Marco Brunettin, LL</t>
+          <t/>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings012024.zip::40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2788 Zahariev Hermes Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Marco Brunettin; Marco Brunettin, LL</t>
+          <t/>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings112023.zip::39739 - Rechnung 231128_2023 vom 28.12.2023, Aufträge 31_23, 32_23, 33_23, 34_23, 50_23, 98_23, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2789 Zahariev TF Touren.pdf</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Marco Brunettin; Marco Brunettin, LL</t>
+          <t/>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings112023.zip::90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2794 Zahariev KFZ Miete.pdf</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t/>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/awbonuses042024.zip::38389 - Vorgangsmappe Lohn - Auszahlungen Inflationsprämie.xlsx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2799 Bearbeitungsgebühr 10.06.2025 Zahariev.pdf</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/awbonusfoodbonus032024.zip::38389 - Vorgangsmappe Lohn - Auszahlungen Inflationsprämie.xlsx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2810 Zahariev TF Touren.pdf</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -1984,7 +1984,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/awbonusfoodbonus032024.zip::38389 - Vorgangsmappe Lohn - Working Hours 03-2024 .xlsx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2811 Zahariev scannermiete.pdf</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2011,61 +2011,61 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t/>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdabrechnungmai2025.zip::gutschrift 66 Mai 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2813 zahariev bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t/>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdabrechnungseptember.zip::Gutschrift 31-2024 Zahariev Martin 30.09.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2814 zahariev bekleidung.pdf</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2075,12 +2075,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t>Dennis Kollmann, Marco Schlüter</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdfwgutschriftrechnungen.zip::gutschrift 05.04. 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157425.pdf</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2092,7 +2092,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t>Dennis Kollmann, Marco Schlüter</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdfwgutschriftrechnungen.zip::Rechnung 2766 Zahariev Hermes Sendungsverlust.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157934.pdf</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2119,61 +2119,61 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t/>
+          <t>Dennis Kollmann, Marco Schlüter</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdfwgutschriftrechnungen.zip::Rechnung 2764 Zahariev Hermes Kleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000826.pdf</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t/>
+          <t>Dennis Kollmann, Marco Schlüter</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdfwgutschriftrechnungen.zip::Rechnung 2765 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000990.pdf</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
+          <t>Dennis Kollmann, Marco Schlüter</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdfwgutschriftrechnungen.zip::Rechnung 2767 Zahariev Hermes Bearbeitungsgebuhr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400001108-1.pdf</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2200,88 +2200,88 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t/>
+          <t>Dennis Kollmann, Marco Schlüter</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgsundrechnungen052025.zip::Rechnung 2788 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400017841.pdf</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t/>
+          <t>Dennis Kollmann, Marco Schlüter</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgsundrechnungen052025.zip::Rechnung 2789 Zahariev TF Touren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400018211.pdf</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t/>
+          <t>Dennis Kollmann, Marco Schlüter</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgsundrechnungen052025.zip::Rechnung 2794 Zahariev KFZ Miete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035414.pdf</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
+          <t>Dennis Kollmann, Marco Schlüter</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgsundrechnungen052025.zip::Rechnung 2799 Bearbeitungsgebühr 10.06.2025 Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035649.pdf</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2308,7 +2308,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>Logistikbetrieb Weißlog, Hohensteiner Str</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgutschriftundrechnungen.zip::Gutschrift 42-2024 Zahariev Martin 30.11.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Docutain Dokument.pdf</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2335,7 +2335,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgutschriftundrechnungen.zip::Rechnung 2014 vom 05.12.2024 Sendungsverlust Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 05.04. 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2362,22 +2362,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2015-07</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgutschriftundrechnungen.zip::Rechnung 2015 07.12.2024 Martin Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 24-2024 Zahariev Martin 31.07.2024.pdf</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgutschriftundrechnungen.zip::Rechnung 2023 vom 07.12.2024  Zahariev HERMES Bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 31-2024 Zahariev Martin 30.09.2024.pdf</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -2416,22 +2416,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t>Goetz, Schneeberg; Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdihreabrechnungsunterlagen012024350690382950.zip::Unternehmerabrechnung - VP 120-2400035414.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 34-2024 Zahariev Martin 04.10.2024.pdf</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2443,7 +2443,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdihreabrechnungsunterlagen012024350690382950.zip::Unternehmerabrechnung - VP 120-2400035649.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 38-2024 Zahariev Martin 31.10.2024.pdf</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2470,7 +2470,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdihreabrechnungsunterlagen0120243506903829501.zip::Unternehmerabrechnung - VP 120-2400000826.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 42-2024 Zahariev Martin 30.11.2024.pdf</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -2497,7 +2497,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdihreabrechnungsunterlagen0120243506903829501.zip::Unternehmerabrechnung - VP 120-2400000990.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 44-2024 Zahariev Martin 31.12.2024.pdf</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -2524,34 +2524,34 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t/>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendengutschrift382024zaharievmartin3.zip::Gutschrift 38-2024 Zahariev Martin 31.10.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 66 Mai 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendengutschrift442024zaharievmartin3.zip::Gutschrift 44-2024 Zahariev Martin 31.12.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 71 2025 zahariev Sendungsverlust.pdf</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendengutschriftapril2025zahariev_pdf.zip::gutschrift April 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift April 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendengutschriftmrz2025zahariev_pdf.zip::gutschrift märz 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift märz 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -2632,34 +2632,34 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t/>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenleistungsnachweismartinzaharievfe.zip::Martin Zahariev Gutschrift 52 28.02.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift Zahariev 74 30.06.2025.pdf</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenleistungsnachweiszaharievjuli2024.zip::Gutschrift 24-2024 Zahariev Martin 31.07.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 48 31.01.2025.pdf</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -2686,34 +2686,34 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t/>
+          <t>2</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t/>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenleistungsnachweiszaharievjuni25s.zip::Gutschrift Zahariev 74 30.06.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 51 17.02.2025.pdf</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievgutschrift4831_01_.zip::Martin Zahariev Gutschrift 48 31.01.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 52 28.02.2025.pdf</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -2740,22 +2740,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2036-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte203608_0.zip::Martin Zahariev Transporte 2036 08.01.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 55 08.03.2025.pdf</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -2767,7 +2767,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2037-08</t>
+          <t>2035-08</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte203608_0.zip::Martin Zahariev Transporte 2037 08.01.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2035 08.01.2025 Hermes Bekleidung.pdf</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -2794,22 +2794,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2038-08</t>
+          <t>2037-08</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte203608_0.zip::Martin Zahariev Transporte 2038 08.01.2025 Bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2037 08.01.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -2821,22 +2821,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2035-08</t>
+          <t>2038-08</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte203608_0.zip::Martin Zahariev Transporte 2035 08.01.2025 Hermes Bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2038 08.01.2025 Bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -2848,7 +2848,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2054-07</t>
+          <t>2055-07</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte205407_0.zip::Martin Zahariev Transporte 2054 07.02.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2055 07.02.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -2875,22 +2875,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2055-07</t>
+          <t>2056-07</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte205407_0.zip::Martin Zahariev Transporte 2055 07.02.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2056 07.02.2025 Bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -2902,22 +2902,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2056-07</t>
+          <t>2057-07</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte205407_0.zip::Martin Zahariev Transporte 2056 07.02.2025 Bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2057 07.02.2025 Hermes Bekleidung.pdf</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -2929,22 +2929,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2057-07</t>
+          <t>2069-08</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte205407_0.zip::Martin Zahariev Transporte 2057 07.02.2025 Hermes Bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2069 08.03.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte207008_0.zip::Martin Zahariev Transporte 2070 08.03.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2070 08.03.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -2983,22 +2983,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2069-08</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte207008_0.zip::Martin Zahariev Transporte 2069 08.03.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2014 vom 05.12.2024 Sendungsverlust Zahariev.pdf</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3010,115 +3010,115 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2015-07</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t/>
+          <t>2</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t/>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenrechnung2778zaharievhermesscanne.zip::Rechnung 2778 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2015 07.12.2024 Martin Zahariev.pdf</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t/>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenrechnung2778zaharievhermesscanne.zip::Rechnung 2777 Zahariev Hermes Unterstützungstouren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2023 vom 07.12.2024  Zahariev HERMES Bekleidung.pdf</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
+          <t/>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenrechnung2778zaharievhermesscanne.zip::Rechnung 2782 Zahariev Hermes Bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2764 Zahariev Hermes Kleidung.pdf</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t/>
+          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdrechnungenaus062025.zip::Rechnung 2814 zahariev bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2766 Zahariev Hermes Sendungsverlust.pdf</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdrechnungenaus062025.zip::Rechnung 2813 zahariev bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2767 Zahariev Hermes Bearbeitungsgebuhr.pdf</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -3145,295 +3145,52 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t/>
+          <t>3</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t/>
+          <t>Chemnitz , Sachs; Motoren-Frech, Uwe; Thomas Frech GbR, Hohensteiner Straße</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdrechnungenaus062025.zip::Rechnung 2811 Zahariev scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/11_Contribution_Lists/RE-53380_2024 13.08.2024 09_17_16.pdf</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t/>
+          <t>3</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t/>
+          <t>Chemnitz , Sachs; Motoren-Frech, Uwe; Thomas Frech GbR, Hohensteiner Straße</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdrechnungenaus062025.zip::Rechnung 2810 Zahariev TF Touren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/11_Contribution_Lists/RE-53652_2024 20.09.2024 10_56_50.pdf</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Boulevard Royal, L; Der Verkäufer behält sich vor, Verarbeitungsaufträge abzulehnen; E-Mail, Fax oder Brief; EE Amsterdam, Niederlande; Grafiken in den vom Verkäufer vorgegebenen Dateiformaten, Formatierungen; Kennedy, L; Reklamationen, Widerrufserklärungen und; Reklamationen, Widerrufserklärungen und -zusendungen oder Gutschriften; Stockholm, Schweden; Urheber-, Marken- und Persönlichkeitsrechte; Versendung, Retouren; Ware, Lieferzeit; Zahlungsabwicklung über die TeamBank AG Nürnberg, Beuthener Straße; Überweisungsgebühren, Wechselkursgebühren</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/ihrebestellung465795beiwebergmbh.zip::agb_doc.pdf</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Herleshausen, Deutschland; Post versandter Brief, Telefax oder E-Mail; Weber GmbH, Sülzbach</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/ihrebestellung465795beiwebergmbh.zip::widerruf_doc.pdf</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/ihrelohnauswertungen.zip::working hours 06.2025  _____.xlsx</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2018-05</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>BIG direkt gesund, Rheinische Straße; Dortmund, Deutschland; Peter Kaetsch, Markus Bäumer</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/ihrelohnauswertungen3333.zip::BIG_Arbeitgeber_SEPA_Lastschriftmandat.pdf</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/ihrelohnauswertungenapril2025.zip::working hours 04.2025.xlsx</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2023-01</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/ihrelohnauswertungendezember2024.zip::working hours 12.2024.xlsx</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/testpayslip.zip::38389 - Vorgangsmappe Lohn - 38389 - Aktualisiert- Auszahlungen Inflationsprämie.xlsx</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/updatedworkinghoursinflationsprmie.zip::38389 - Vorgangsmappe Lohn - Auszahlungen Inflationsprämie.xlsx</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2024-01</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Akkreditiert durch DAkkS, Registriernummer; Berlin-Charlottenburg, HRB; Präqualifikation Kurier-, Express- und Paketdienstleistern i; ZERTIFIZIERUNG BAU GMBH, Kronenstraße</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/wgprqualifikationkepkdnr_60222rechnungjahresgeb.zip::20240123_60222_10160_Rechnung.pdf</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>

--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/employee_timeline.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/employee_timeline.xlsx
@@ -45,17 +45,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
+          <t>Euro, Tsd; Kalev, Krasimir; Kilometer, St; Metodiev, Nikolay; Name; Tage, Km; Tanev, Martin Rangelov; Tausend Euro, Mio; Yordanov, Radi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_01-2024_DivAuswertungen_DivMitarbeiter_2Z1 (2)-1.pdf</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -67,22 +67,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
+          <t>Euro, Tsd; Kalev, Krasimir; Kilometer, St; Metodiev, Nikolay; Name; Tage, Km; Tanev, Martin Rangelov; Tausend Euro, Mio; Yordanov, Radi</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00107_QZ1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_01-2024_DivAuswertungen_DivMitarbeiter_2Z1.pdf</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -94,22 +94,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2021-02</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ADAC, Hansastr; MP, MARTIN ZAHARIEVSOZIALVERSICHER; Rundfunk ARD, ZDF; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+          <t>Dankin, Georgi; Euro, Tsd; Kilometer, St; Kostov, Ventsislav; Madzharov, Atanas Emilov; Metodiev, Nikolay; Name; Simeonov, Vasil; Stefanova, Petya; Tage, Km; Tausend Euro, Mio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_02-2024_DivAuswertungen_00006_5Z1.pdf</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -121,22 +121,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; Burger King, FOOD STAR GmbH; GLOBUS SBW, CHEMNITZ; Globus SBW, Chemnitz; Gutschrift Darling züruck , Danke Mersi; MP, INH; MP, MARTIN ZAHARIEVSOZIALVERSICHER; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+          <t>Dankin, Georgi; Euro, Tsd; Kilometer, St; Kostov, Ventsislav; Madzharov, Atanas Emilov; Name; Petrov, Kristiyan; Tage, Km; Tausend Euro, Mio; Todorov, Stoyan; Todorov, Vasilios</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_03-2024_DivAuswertungen_DivMitarbeiter_8Z1.pdf</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -148,22 +148,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ADAC Versicherung AG, Hansastr; ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; Burger King, FOOD STAR GmbH; EUR, SOL; KG, Ihr Einkauf bei Parf; MP, INH; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+          <t>Dankin, Georgi; Euro, Tsd; Kilometer, St; Kostov, Ventsislav; Madzharov, Atanas Emilov; Name; Petrov, Kristiyan; Tage, Km; Tausend Euro, Mio; Todorov, Stoyan; Todorov, Vasilios</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2023 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_03-2024_DivAuswertungen_DivMitarbeiter_8Z1__copy2.pdf</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -175,22 +175,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ADAC, Hansastr; MP, MARTIN ZAHARIEVSOZIALVERSICHER; Rundfunk ARD, ZDF; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+          <t>Euro, Tsd; Kilometer, St; Mihaila, Stefan; Name; Petrov, Kristiyan; Tage, Km; Tausend Euro, Mio</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_04-2024_DivAuswertungen_DivMitarbeiter_BZ1.pdf</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -202,22 +202,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; BUONO, CHEMNITZ; GLOBUS SBW, CHEMNITZ; Gutschrift Darling züruck , Danke Mersi; MP, INH; Reece Upadhyay, Ihr Einkauf bei R; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+          <t>Euro, Tsd; Kilometer, St; Metodiev, Nikolay; Name; Tage, Km; Tausend Euro, Mio; Todorov, Vasilios</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_05-2024_DivAuswertungen_DivMitarbeiter_EZ1.pdf</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -229,22 +229,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ADAC, Hansastr; ARD, ZDF; DANKE, IHR LIDL; MP, MARTIN ZAHARIEVSOZIALVERSICHER; Simply NetTrade GmbH, Ihr Einkauf bei Simply NetTrade Gmb; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+          <t>Euro, Tsd; Kilometer, St; Madzharov, Atanas Emilov; Milcheva, Iveta; Name; Stefanova, Petya; Tage, Km; Tausend Euro, Mio</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_06-2024_DivAuswertungen_DivMitarbeiter_HZ1.pdf</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -256,22 +256,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTO CENTER SUED, CHEMNITZ; BRAZIL OHG, CHEMNITZ; BUONO, CHEMNITZ; MP, INH; Reece Upadhyay, Ihr Einkauf bei R; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+          <t>Abfindung, Entschädigung oder ähnliche Leistung wegen der Beendigung desWenn ja; Abfindung, Entschädigung oder ähnlichen Leistung zulässig; Der Arbeitgeber hätte das Arbeitsverhältnis gekündigt; Euro, Tsd; Kilometer, St; Revolut Bank, Berlin; Tage, Km; Tausend Euro, Mio</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_06_2025_Div_Auswertungen_Div_Mitarbeiter.pdf</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -283,7 +283,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2021-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -293,12 +293,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ADAC, Hansastr; ARD, ZDF; Burger King, FOOD STAR GmbH; DANKE, IHR LIDL; MP, MARTIN ZAHARIEVSOZIALVERSICHER; Simply NetTrade GmbH, Ihr Einkauf bei Simply NetTrade Gmb; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+          <t>Dankin, Georgi; Dimitrov, Neycho; Euro, Tsd; Kilometer, St; Name; Tage, Km; Tausend Euro, Mio</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_07-2024_DivAuswertungen_DivMitarbeiter_KZ1.pdf</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -310,22 +310,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTO CENTER SUED, CHEMNITZ; MP, INH; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_08-2024_Brutto_NettoProbe_00074_NZ1.pdf</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -337,22 +337,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ADAC, Hansastr; ARD, ZDF; BRAZIL OHG, CHEMNITZ; Burger King, FOOD STAR GmbH; DANKE, IHR LIDL; MP, MARTIN ZAHARIEVSOZIALVERSICHER; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/09-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_08-2024_Brutto_NettoProbe_00098_NZ1.pdf</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -364,22 +364,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ADAC, Hansastr; AGIP,ANSBACHER STR; AGIP,NUERNBERG; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTO CENTER SUED, CHEMNITZ; BUONO, CHEMNITZ; Burger King, FOOD STAR GmbH; MP, INH; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/10-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00051_QZ1.pdf</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -391,22 +391,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ADAC, Hansastr; ARD, ZDF; FAVORIT MP, MARTINSOZIALVERSICHERU; MP, MARTIN ZAHARIEVSOZIALVERSICHER; MP, MARTIN ZAHARIEVSOZIALVERSICHERU; ZAHARIEV, MARTIN ADAC VERSICHER; Überweisung Kirev,Kosta</t>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/11-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_Brutto_NettoProbe_00107_QZ1.pdf</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -418,22 +418,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ADAC, Hansastr; ARD, ZDF; Burger King, FOOD STAR GmbH; EUR, UMS; FAVORIT MP, MARTINSOZIALVERSICHERU; GLOBUS SBW, CHEMNITZ; Globus SBW, Chemnitz; MP, MARTIN ZAHARIEVSOZIALVERSICHER; MP, MARTIN ZAHARIEVSOZIALVERSICHERU; ZAHARIEV, MARTIN ADAC VERSICHER; Überweisung Kirev,Kosta</t>
+          <t>Bogdan, Cosmin-Florin; Dimitrov, Neycho; Euro, Tsd; Genchev, Lyudmil; Ignat, Petronel; Kilometer, St; Name; Tage, Km; Tausend Euro, Mio; Vasilev, Georgi</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_09-2024_DivAuswertungen_DivMitarbeiter_QZ1.pdf</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -445,22 +445,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ADAC, Hansastr; AGIP,ANSBACHER STR; AGIP,NUERNBERG; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTO CENTER SUED, CHEMNITZ; BUONO, CHEMNITZ; Burger King, FOOD STAR GmbH; KG, Ihr Einkauf bei Parf; MP, INH; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_12-2023_Brutto_NettoProbe_00025_ZZ1.pdf</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -472,22 +472,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
+          <t>Dimitrov, Neycho; Euro, Tsd; Kalev, Krasimir; Kilometer, St; Name; Stefanova, Petya; Tage, Km; Tanev, Martin Rangelov; Tausend Euro, Mio; Yordanov, Radi</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2024_Brutto_Netto_00090_X0B.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/10001_12-2023_DivAuswertungen_DivMitarbeiter_ZZ1.pdf</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -499,61 +499,61 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2018-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>Ort, Datum Firmenstempel</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/312_neut__Verdienstbescheinigung_Brutto_Netto_01_08_2023_-_31_07_2024.pdf</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t/>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Betreuung durch den ASD, Bescheid; EUR Warenlieferung, Forderung aus; Feuerwehr Zwickau, Kennzeichen; Ieva Meilutyte, Stefan Mihaila; Säumniszuschläge, Kosten; Säumniszuschläge, Nachzahlungszinsen und; Säumniszuschläge, Zinsen; Ventsislav Kostov, Ionel Neamtu; ZV-Sache, AG Chemnitz; Zahariev, Martin</t>
+          <t/>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Health Security.pdf</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Vasilev_Test Pay Slip.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_April_2025.pdf</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -580,7 +580,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/38389 - Vorgangsmappe Lohn - 38389 - Aktualisiert- Auszahlungen Inflationsprämie.xlsx</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Juli_2024.pdf</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -607,22 +607,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Marco Brunettin; Marco Brunettin, LL</t>
+          <t>Abfindung, Entschädigung oder ähnliche Leistung wegen der Beendigung desWenn ja; Abfindung, Entschädigung oder ähnlichen Leistung zulässig; Der Arbeitgeber hätte das Arbeitsverhältnis gekündigt; Euro, Tsd; Kilometer, St; Revolut Bank, Berlin; Tage, Km; Tausend Euro, Mio</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Juli_2025.pdf</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -634,22 +634,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t/>
+          <t>2000-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boulevard Royal, L; Der Verkäufer behält sich vor, Verarbeitungsaufträge abzulehnen; E-Mail, Fax oder Brief; EE Amsterdam, Niederlande; Grafiken in den vom Verkäufer vorgegebenen Dateiformaten, Formatierungen; Kennedy, L; Reklamationen, Widerrufserklärungen und; Reklamationen, Widerrufserklärungen und -zusendungen oder Gutschriften; Stockholm, Schweden; Urheber-, Marken- und Persönlichkeitsrechte; Versendung, Retouren; Ware, Lieferzeit; Zahlungsabwicklung über die TeamBank AG Nürnberg, Beuthener Straße; Überweisungsgebühren, Wechselkursgebühren</t>
+          <t>Abfindung, Entschädigung oder ähnliche Leistung wegen der Beendigung desWenn ja; Abfindung, Entschädigung oder ähnlichen Leistung zulässig; Arbeitslohn für mehrere Kalenderjahre, Entschädigungen z; Catana, Stefan-Andrei; Der Arbeitgeber hätte das Arbeitsverhältnis gekündigt; Dudas, Laci; Euro, Tsd; Feraru, Andrei; Jaleru, Marius-Gabrie; Kilometer, St; Kitanov, Todor; Kostova, Sofia; Madzharov, Atanas Emi; Meilutyte, Ieva; Petrea, Ciprian-Nicol; Revolut Bank, Berlin; Savin, Andrei-Antonio; Tage, Km; Tausend Euro, Mio; Vasilev, Georgi</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/agb_doc.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Juli_2025__copy2.pdf</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -661,22 +661,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Autoverwertung-Oskar, Schulstr</t>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Rechnung_RE058675_11.08.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Juni_2025.pdf</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -688,22 +688,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Herleshausen, Deutschland; Post versandter Brief, Telefax oder E-Mail; Weber GmbH, Sülzbach</t>
+          <t>Aufhebungsvertrag, AG hätte nicht oder nicht zum selben Zeitpunkt gek</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/widerruf_doc.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Mai_2024-1.pdf</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -715,130 +715,130 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t/>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Parfumerie Douglas GmbH, Ihr Eink auf bei Parfumeri; Parfumerie Douglas GmbH, Ihr Einkau; Skull Sh aver EU Ltd, Ihr Ei; Skull Shaver EU Ltd, Ihr Einkauf bei Skull Shaver EU Lt</t>
+          <t/>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/01-2023 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Mai_2024.pdf</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2022-02</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t/>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ALEX Chemnitz, Galerie Roter Turm; Burger King, FOOD STAR GmbH; Limited, Ih</t>
+          <t/>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/02-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_März_2025.pdf</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t/>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ALEX Chemnitz, Galerie Roter Turm; AUTODOC AG, Ihr Einkau; Burger King, FOOD STAR GmbH; Dott, Ihr Einkauf bei Dott; EUR, Tra; Limited, Ih; Tier Mobility GmbH, Ihr Einkauf b</t>
+          <t/>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/04-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_November_2024-1.pdf</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2022-06</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t/>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ALEX Chemnitz, Galerie Roter Turm; AUTO CENTER SUED, CHEMNITZ; AUTODOC AG, Ihr Einkau; Dott, Ihr Einkauf bei Dott; Tier Mobility GmbH, Ihr Einkauf b</t>
+          <t/>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/06-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_November_2024.pdf</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm</t>
+          <t>Ignat, Petronel; Mihaylov, Bozhidar; Petrov, Kristiyan; Vasilev, Georgi</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/07-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Oktober_2024.pdf</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -850,22 +850,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ADAC, Hansastr; AG, Ihr Einkauf bei AUTODOC AG; ALEX Chemnitz, Galerie Roter Turm</t>
+          <t>Andrunachie, Ionut-Cr; Asenov, Veselin; Bimbalov, Atanas; Bogaevski, Petar N; Caciulescu, Andrei-Cosmi; Chakarov, Svetlomir; Dankin, Georgi; Dimitrov, Neycho; Dragan, Titus-Andrei; Genchev, Lyudmil; Genov, Petar N; Georgiev, Emil; Kalev, Krasimir; Kitanov, Todor; Kostov, Ventsislav; Krumov, Petar; Madzharov, Atanas Emilov; Metodiev, Nikolay; Mihaila, Stefan; Milcheva, Iveta; Panayotov, Momchil; Petrov, Kristiyan; Simeonov, Vasil; Sokolarski, Stanislav; Stefanova, Petya; Stefanova, Petya N; Tanev, Martin Rangelov; Taskov, Rumen; Todorov, Stoyan; Todorov, Vasilios; Turchalieva, Maria-Desis; Vasilev, Martin; Yordanov, Radi; Yordanov, Radi N</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Pay Roll 12.2023.pdf</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -877,22 +877,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2022-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AG, Ihr Einkauf bei AUTODOC AG; EU Ltd, Ihr Einkauf bei Skull; GmbH, Ihr Einkauf bei Parfumerie Do; Parfumerie Douglas GmbH, Ihr Eink</t>
+          <t>Revolut Bank, Berlin</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/12-2022 #9120.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Salaries.pdf</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -904,76 +904,76 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t/>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Akkreditiert durch DAkkS, Registriernummer; Berlin-Charlottenburg, HRB; Präqualifikation Kurier-, Express- und Paketdienstleistern i; ZERTIFIZIERUNG BAU GMBH, Kronenstraße</t>
+          <t/>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/20240123_60222_10160_Rechnung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Seizures.pdf</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Timothy Grygotis, Julia von SpechtSitz</t>
+          <t/>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102600491.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Zoll Kitanov.pdf</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Timothy Grygotis, Julia von SpechtSitz</t>
+          <t>Asenov, Veselin; Bimbalov, Atanas; Bogaevski, Petar; Caciulescu, Andrei-Cosmi; Chakarov, Svetlomir; Dankin, Georgi; Dimitrov, Neycho; Dragan, Titus-Andrei; Genchev, Lyudmil; Georgiev, Emil; Ivanova, Miroslava Angel; Kalev, Krasimir; Kalev, Krasimir NVJ; Kitanov, Todor; Kostov, Ventsislav; Krumov, Petar; Madzharov, Atanas Emilov; Metodiev, Nikolay; Mihaila, Stefan; Mihaylov, Bozhidar; Milcheva, Iveta; Panayotov, Momchil; Petrov, Kristiyan; Simeonov, Vasil; Sokolarski, Stanislav; Stefanova, Petya; Tanev, Martin Rangelo NVJ; Tanev, Martin Rangelov; Taskov, Rumen; Todirascu, Irinel Costel; Todorov, Stoyan; Todorov, Vasilios; Turchalieva, Maria-Desis; Vasilev, Martin; Yordanov, Radi</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102659867.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 01-2024.pdf</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -985,22 +985,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Timothy Grygotis, Julia von SpechtSitz</t>
+          <t>Andrunachie, Ionut-Crist; Arbone, Alexandru-Stefan; Aufhebungsvertrag, AG hätte nicht oder nicht zum selben Zeitpunkt gek; Bogdan, Cosmin-Florin; Buricel, Nicolae-Mihai; Clanetariu, Cosmin-Ionut; Clanetariu, Vasile-Costi; Coretchi, Ion; Dobrescu, Andrei; Dragan, Titus-Andrei; Dudas, Laci; Georgiev, Emil; Grigorescu, Stefan-Vasil; Ignat, Petronel; Kitanov, Todor; Kostova, Sofia; Madzharov, Atanas Emilov; Meilutyte, Ieva; Metodiev, Nikolay; Mihaila, Stefan; Mihaylov, Bozhidar; Milcheva, Iveta; Musteate, Andrei-Nicolae; Neamtu, Ionel; Petrea, Ciprian-Nicolae; Petrov, Kristiyan; Radulin, Raul-Constantin; Raicu, Costel-Dan; Sandu, Narcis-Ionut; Savin, Andrei-Antonio; Simeonov, Vasil; Stasiulis, Ramunas; Stefanov, Georgi; Todirascu, Irinel Costel; Todorov, Stoyan; Trifonov, Preslav; Vasilev, Georgi; Vladutu, Dan-Constantin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102665850.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 01-2025.pdf</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1012,22 +1012,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Timothy Grygotis, Julia von SpechtSitz</t>
+          <t>Asenov, Veselin; Bimbalov, Atanas N; Bogaevski, Petar; Caciulescu, Andrei-Cosmi; Dankin, Georgi; Dimitrov, Neycho; Dobrescu, Andrei; Dragan, Titus-Andrei; Genchev, Lyudmil; Georgiev, Emil; Ivanova, Miroslava Angel; Kalev, Krasimir; Kitanov, Todor; Koprivarov, Kiril; Kostov, Ventsislav; Krumov, Petar; Lacatusu, Marius-Iulian; Madzharov, Atanas Emilov; Metodiev, Nikolay; Mihaila, Stefan; Mihaylov, Bozhidar; Milcheva, Iveta; Panayotov, Momchil; Petrov, Kristiyan; Simeonov, Vasil; Sokolarski, Stanislav; Stefanova, Petya; Tanev, Martin Rangelov; Taskov, Rumen; Todirascu, Irinel Costel; Todorov, Stoyan; Todorov, Vasilios; Trifonov, Preslav; Turchalieva, Maria-Desis; Vasilev, Georgi; Vasilev, Martin; Yordanov, Radi</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102698674.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 02-2024.pdf</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1039,22 +1039,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Andreas Weber, Horst WeberHandelsregister</t>
+          <t>Andrunachie, Ionut-Cris N; Arbone, Alexandru-Stefa N; Aufhebungsvertrag, AG hätte nicht oder nicht zum selben Zeitpunkt gek; Bogdan, Cosmin-Florin N; Boroda, Catalin; Buricel, Nicolae-Mihai N; Clanetariu, Cosmin-Ionu N; Coretchi, Ion N; Dobrescu, Andrei N; Dragan, Titus-Andrei N; Dudas, Laci N; Georgiev, Emil N; Grigorescu, Stefan-Vasi N; Kitanov, Todor N; Kostova, Sofia N; Lupascu, Florin-Madalin; Madzharov, Atanas Emilo N; Meilutyte, Ieva N; Mihaila, Stefan N; Mihaylov, Bozhidar N; Milcheva, Iveta N; Musteate, Andrei-Nicola N; Neamtu, Ionel N; Petrea, Ciprian-Nicolae N; Petrov, Kristiyan N; Radulin, Raul-Constanti N; Raicu, Costel-Dan N; Savin, Andrei-Antonio N; Simeonov, Vasil N; Stefanov, Georgi N; Todirascu, Irinel Coste N; Todorov, Stoyan NVJ; Trifonov, Preslav N; Vasilev, Georgi N; Vladutu, Dan-Constantin N</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 02-2025.pdf</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1066,22 +1066,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Andreas Weber, Horst WeberHandelsregister</t>
+          <t>Asenov, Veselin; Bogaevski, Petar; Dankin, Georgi; Dimitrov, Neycho; Dobrescu, Andrei; Dragan, Titus-Andrei; Genchev, Lyudmil; Georgiev, Emil; Grigorescu, Stefan-Vasil; Ivanova, Miroslava Angel; Kitanov, Todor; Koprivarov, Kiril; Kostov, Ventsislav; Krumov, Petar; Lacatusu, Marius-Iulian; Madzharov, Atanas Emilov; Metodiev, Nikolay; Mihaila, Stefan; Mihaylov, Bozhidar; Milcheva, Iveta; Panayotov, Momchil; Petrov, Kristiyan; Simeonov, Vasil N; Sokolarski, Stanislav; Stefanova, Petya; Taskov, Rumen; Todirascu, Irinel Costel; Todorov, Stoyan; Todorov, Vasilios; Trifonov, Preslav; Turchalieva, Maria-Desis; Vasilev, Georgi N; Vasilev, Martin N; Yordanov, Radi</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 03-2024.pdf</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1093,22 +1093,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Timothy Grygotis, Julia von Specht</t>
+          <t>Andrunachie, Ionut-Crist; Arbone, Alexandru-Stefan; Aufhebungsvertrag, AG hätte nicht oder nicht zum selben Zeitpunkt gek; Bogdan, Cosmin-Florin; Boroda, Catalin; Clanetariu, Cosmin-Ionut; Coretchi, Ion; Dobrescu, Andrei N; Dragan, Titus-Andrei; Dudas, Laci; Feraru, Andrei; Georgiev, Emil; Kitanov, Todor; Kostova, Sofia N; Lupascu, Florin-Madalin; Madzharov, Atanas Emilov; Meilutyte, Ieva NVJ; Mihaila, Stefan; Mihaylov, Bozhidar N; Milcheva, Iveta; Musteate, Andrei-Nicolae; Neamtu, Ionel; Petrea, Ciprian-Nicolae; Petrov, Kristiyan; Radulin, Raul-Constantin; Raicu, Costel-Dan; Savin, Andrei-Antonio; Simeonov, Vasil; Stefanov, Georgi; Trifonov, Preslav; Vasilev, Georgi; Vladutu, Dan-Constantin</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-1.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 03-2025.pdf</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1120,22 +1120,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Timothy Grygotis, Julia von Specht</t>
+          <t>Bogaevski, Petar; Dankin, Georgi; Dimitrov, Neycho N; Dobrescu, Andrei; Dragan, Titus-Andrei; Genchev, Lyudmil; Georgiev, Emil; Grigorescu, Stefan-Vasil; Ivanova, Miroslava Angel; Kitanov, Todor; Kostov, Ventsislav; Krumov, Petar; Lacatusu, Marius-Iulian; Madzharov, Atanas Emilov; Metodiev, Nikolay; Mihaila, Stefan; Mihaylov, Bozhidar; Milcheva, Iveta; Panayotov, Momchil; Petrov, Kristiyan; Simeonov, Vasil; Sokolarski, Stanislav; Stefanova, Petya; Taskov, Rumen; Todirascu, Irinel Costel; Todorov, Stoyan NVJ; Todorov, Vasilios; Trifonov, Preslav; Turchalieva, Maria-Desis; Vasilev, Georgi N; Vasilev, Martin; Vladutu, Dan-Constantin; Yordanov, Radi</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-2.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 04-2024.pdf</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1147,22 +1147,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Timothy Grygotis, Julia von Specht</t>
+          <t>Abfindung, Entschädigung oder ähnliche Leistung wegen der Beendigung desWenn ja; Abfindung, Entschädigung oder ähnlichen Leistung zulässig; Andrunachie, Ionut-Crist; Arbeitslohn für mehrere Kalenderjahre, Entschädigungen z; Arbone, Alexandru-Stef; Catana, Stefan-Andrei; Clanetariu, Cosmin-Ion; Coretchi, Ion; Der Arbeitgeber hätte das Arbeitsverhältnis gekündigt; Dragan, Titus-Andrei; Dudas, Laci; Euro, Tsd; Feraru, Andrei; Georgiev, Emil; Jaleru, Marius-Gabriel; Kilometer, St; Kitanov, Todor; Kostova, Sofia; Lupascu, Florin-Madalin; Madzharov, Atanas Emilov; Meilutyte, Ieva; Mihaila, Stefan; Mihaylov, Bozhidar; Milcheva, Iveta; Musteate, Andrei-Nicolae; Neamtu, Ionel; Petrea, Ciprian-Nicolae; Petrov, Kristiyan; Radulin, Raul-Constantin; Raicu, Costel-Dan; Revolut Bank, Berlin; Savin, Andrei-Antonio; Stefanov, Georgi; Tage, Km; Tausend Euro, Mio; Trifonov, Preslav N; Vasilev, Georgi; Vladutu, Dan-Constantin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 04-2025.pdf</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1174,22 +1174,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avis Budget Autovermietung Verwaltungsgesellschaft mbH, Oberursel; KG, Amtsgericht Bad Homburg v; OBERURSEL, GERMANY; Sollten Sie Fragen, Wünsche oder auch Beanstandungen haben; Wir hoffen, Sie bald wieder bei uns begrüssen zu dürfen; ZAHARIEV,MARTIN; ZAHARIEV,MARTIN Gefahrene Entfernung</t>
+          <t>Bogaevski, Petar; Dankin, Georgi; Dimitrov, Neycho; Dobrescu, Andrei; Dragan, Titus-Andrei; Genchev, Lyudmil; Georgiev, Emil; Grigorescu, Stefan-Vasil; Kitanov, Todor; Kostov, Ventsislav; Kostova, Sofia; Krumov, Petar; Lacatusu, Marius-Iulian; Madzharov, Atanas Emilov; Metodiev, Nikolay; Mihaila, Stefan; Mihaylov, Bozhidar N; Milcheva, Iveta; Panayotov, Momchil; Petrov, Kristiyan; Simeonov, Vasil; Sokolarski, Stanislav; Stasiulis, Ramunas; Stefanova, Petya; Taskov, Rumen; Todirascu, Irinel Costel; Todorov, Stoyan; Todorov, Vasilios; Trifonov, Preslav; Turchalieva, Maria-Desis; Vasilev, Georgi; Vasilev, Martin N; Vladutu, Dan-Constantin; Yordanov, Radi</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/307538032.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 05-2024.pdf</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1201,22 +1201,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2001-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Marco Brunettin; Marco Brunettin, LL</t>
+          <t>Andrunachie, Ionut-Crist; Arbeitslohn für mehrere Kalenderjahre, Entschädigungen z; Catana, Stefan-Andrei; Coretchi, Ion; Dragan, Titus-Andrei; Dudas, Laci; Euro, Tsd; Feraru, Andrei; Georgiev, Emil; Jaleru, Marius-Gabriel; Kilometer, St; Kitanov, Todor; Kostova, Sofia; Lupascu, Florin-Madal; Madzharov, Atanas Emilov; Meilutyte, Ieva; Mihaila, Stefan; Mihaylov, Bozhidar; Milcheva, Iveta; Musteate, Andrei-Nicolae; Neamtu, Ionel; Petrea, Ciprian-Nicolae; Petrov, Kristiyan; Radulin, Raul-Constantin; Raicu, Costel-Dan; Revolut Bank, Berlin; Savin, Andrei-Antonio NVJ; Stefanov, Georgi; Tage, Km; Tausend Euro, Mio; Vasilev, Georgi; Vladutu, Dan-Constantin</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/39739 - Rechnung 231128_2023 vom 28.12.2023, Aufträge 31_23, 32_23, 33_23, 34_23, 50_23, 98_23, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 05-2025.pdf</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1228,22 +1228,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Marco Brunettin; Marco Brunettin, LL</t>
+          <t>Bogaevski, Petar; Dankin, Georgi; Dimitrov, Neycho; Dobrescu, Andrei; Dragan, Titus-Andrei; Genchev, Lyudmil; Georgiev, Emil; Grigorescu, Stefan-Vasil; Ignat, Petronel; Kitanov, Todor; Kostov, Ventsislav; Kostova, Sofia; Krumov, Petar; Madzharov, Atanas Emilo N; Madzharov, Atanas Emilov; Metodiev, Nikolay; Mihaila, Stefan; Mihaylov, Bozhidar; Milcheva, Iveta; Panayotov, Momchil; Petrov, Kristiyan; Simeonov, Vasil; Sokolarski, Stanislav; Stasiulis, Ramunas; Stefanova, Petya; Taskov, Rumen; Todirascu, Irinel Costel; Todorov, Stoyan; Todorov, Vasilios; Trifonov, Preslav; Turchalieva, Maria-Desis; Vasilev, Georgi; Vladutu, Dan-Constantin</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 06-2024.pdf</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1255,22 +1255,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2000-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t>Abfindung, Entschädigung oder ähnliche Leistung wegen der Beendigung desWenn ja; Abfindung, Entschädigung oder ähnlichen Leistung zulässig; Andrunachie, Ionut-Crist; Arbeitslohn für mehrere Kalenderjahre, Entschädigungen z; Aufhebungsvertrag, AG hätte nicht oder nicht zum selben Zeitpunkt gek; Catana, Stefan-Andrei; Der Arbeitgeber hätte das Arbeitsverhältnis gekündigt; Dudas, Laci; Euro, Tsd; Feraru, Andrei; Georgiev, Emil; Jaleru, Marius-Gabriel; Kilometer, St; Kitanov, Todor; Kostova, Sofia; Madzharov, Atanas Emilov; Meilutyte, Ieva; Mihaila, Stefan; Milcheva, Iveta; Petrea, Ciprian-Nicol NVJ; Petrov, Kristiyan; Revolut Bank, Berlin; Savin, Andrei-Antonio; Stefanov, Georgi; Tage, Km; Tausend Euro, Mio; Vasilev, Georgi; Vladutu, Dan-Constantin</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 06-2025.pdf</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1282,22 +1282,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t>Bogaevski, Petar; Dankin, Georgi; Dimitrov, Neycho; Dobrescu, Andrei; Dragan, Titus-Andrei; Dudas, Laci; Genchev, Lyudmil; Georgiev, Emil; Grigorescu, Stefan-Vasil; Ignat, Petronel; Kitanov, Todor; Kostov, Ventsislav; Kostova, Sofia; Krumov, Petar; Metodiev, Nikolay; Mihaila, Stefan; Mihaylov, Bozhidar; Milcheva, Iveta; Neamtu, Ionel; Panayotov, Momchil; Petrov, Kristiyan; Simeonov, Vasil; Sokolarski, Stanislav; Stasiulis, Ramunas; Stefanov, Georgi; Todirascu, Irinel Costel; Todorov, Stoyan; Todorov, Vasilios; Trifonov, Preslav; Turchalieva, Maria-Desis; Vasilev, Georgi; Vladutu, Dan-Constantin; Yoshev, Iliyan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 07-2024.pdf</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1309,22 +1309,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t>Andrunachie, Ionut-Crist; Bogaevski, Petar; Bogdan, Cosmin-Florin; Dankin, Georgi; Dimitrov, Neycho; Divile, Ciprian; Dobrescu, Andrei; Dragan, Titus-Andrei; Dudas, Laci; Dunaroae, Dumitru-Marian; Genchev, Lyudmil; Georgiev, Emil; Grigorescu, Stefan-Vasil; Ignat, Petronel; Kitanov, Todor; Kostov, Ventsislav; Kostova, Sofia; Krumov, Petar; Lacatusu, Marius-Iulian; Metodiev, Nikolay; Mihaila, Stefan; Mihaylov, Bozhidar; Milcheva, Iveta; Neamtu, Ionel N; Oprea, Constantin-Andrei; Panayotov, Momchil; Petrov, Kristiyan; Savin, Andrei-Antonio; Simeonov, Vasil; Sokolarski, Stanislav; Stasiulis, Ramunas; Stefanov, Georgi; Todirascu, Irinel Costel; Todorov, Stoyan; Todorov, Vasilios; Trifonov, Preslav; Vasilev, Georgi; Vladutu, Dan-Constantin; Yoshev, Iliyan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 08-2024.pdf</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1336,22 +1336,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t>Andrunachie, Ionut-Cris N; Arbone, Alexandru-Stefan; Bogdan, Cosmin-Florin; Buricel, Nicolae-Mihai; Clanetariu, Cosmin-Ionut; Clanetariu, Vasile-Costi; Coretchi, Ion; Dankin, Georgi; Dimitrov, Neycho; Divile, Ciprian; Dobrescu, Andrei; Dragan, Titus-Andrei; Dudas, Laci; Dunaroae, Dumitru-Marian; Genchev, Lyudmil; Georgiev, Emil; Grigorescu, Stefan-Vasil; Ignat, Petronel; Kitanov, Todor; Kostov, Ventsislav; Lacatusu, Marius-Iulia; Metodiev, Nikolay; Mihaila, Stefan; Mihaylov, Bozhidar; Milcheva, Iveta; Musteate, Andrei-Nicolae; Neamtu, Ionel; Oprea, Constantin-Andrei; Panayotov, Momchil; Petrov, Kristiyan; Sandu, Narcis-Ionut; Savin, Andrei-Antonio N; Simeonov, Vasil; Stasiulis, Ramunas; Stefanov, Georgi; Todirascu, Irinel Costel; Todorov, Stoyan; Todorov, Vasilios; Trifonov, Preslav; Vasilev, Georgi; Vladutu, Dan-Constantin</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 09-2024.pdf</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1363,22 +1363,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t>Andrunachie, Ionut-Crist; Arbone, Alexandru-Stefan; Bogdan, Cosmin-Florin; Buricel, Nicolae-Mihai; Clanetariu, Cosmin-Ionut; Clanetariu, Vasile-Costi; Coretchi, Ion; Dimitrov, Neycho; Dobrescu, Andrei; Dragan, Titus-Andrei N; Dudas, Laci; Dunaroae, Dumitru-Marian; Georgiev, Emil; Grigorescu, Stefan-Vasil; Ignat, Petronel; Ignat, Petronel N; Kitanov, Todor; Meilutyte, Ieva; Metodiev, Nikolay; Mihaila, Stefan; Mihaylov, Bozhidar; Milcheva, Iveta; Musteate, Andrei-Nicolae; Neamtu, Ionel; Oprea, Constantin-Andr; Petrov, Kristiyan; Raicu, Costel-Dan; Sandu, Narcis-Ionut; Savin, Andrei-Antonio; Simeonov, Vasil; Stasiulis, Ramunas; Stefanov, Georgi; Todirascu, Irinel Costel; Todorov, Stoyan; Trifonov, Preslav N; Vasilev, Georgi; Vladutu, Dan-Constantin</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 10-2024.pdf</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1390,22 +1390,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; EURPQ, Matodiev wage statement; Marco Brunettin; Marco Brunettin, LL; Stefanova, Yordanov</t>
+          <t>Andrunachie, Ionut-Crist; Arbone, Alexandru-Stefan; Bogdan, Cosmin-Florin; Buricel, Nicolae-Mihai; Clanetariu, Cosmin-Ionut; Clanetariu, Vasile-Costi; Coretchi, Ion; Dimitrov, Neycho N; Dobrescu, Andrei N; Dragan, Titus-Andrei; Dudas, Laci; Dunaroae, Dumitru-Mar; Georgiev, Emil; Grigorescu, Stefan-Vasi N; Ignat, Petronel; Kitanov, Todor; Madzharov, Atanas Emilov; Meilutyte, Ieva; Metodiev, Nikolay; Mihaila, Stefan; Mihaylov, Bozhidar; Milcheva, Iveta; Musteate, Andrei-Nicolae; Neamtu, Ionel; Petrea, Ciprian-Nicolae; Petrov, Kristiyan; Radulin, Raul-Constantin; Raicu, Costel-Dan; Sandu, Narcis-Ionut; Savin, Andrei-Antonio; Simeonov, Vasil; Stasiulis, Ramunas; Stefanov, Georgi; Todirascu, Irinel Costel; Todorov, Stoyan N; Trifonov, Preslav; Vasilev, Georgi; Vladutu, Dan-Constantin; Vladutu, Dan-Constantin N</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 11-2024.pdf</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1417,22 +1417,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t>Andrunachie, Ionut-Crist; Andrunachie, Ionut-Cristian; Arbone, Alexandru-Stefan; Aufhebungsvertrag, AG hätte nicht oder nicht zum selben Zeitpunkt gek; Bogdan, Cosmin-Florin; Buricel, Nicolae-Mihai; Clanetariu, Cosmin-Ionut; Clanetariu, Vasile-Costi; Clanetariu, Vasile-Costinel; Coretchi, Ion; Dobrescu, Andrei; Dragan, Titus-Andrei; Dudas, Laci; Georgiev, Emil; Grigorescu, Stefan-Vas; Ignat, Petronel; Kitanov, Todor; Madzharov, Atanas Emilov; Meilutyte, Ieva; Metodiev, Nikolay; Mihaila, Stefan; Mihaylov, Bozhidar; Milcheva, Iveta; Musteate, Andrei-Nicolae; Neamtu, Ionel; Petrea, Ciprian-Nicolae; Petrov, Kristiyan; Radulin, Raul-Constantin; Raicu, Costel-Dan; Sandu, Narcis-Ionut; Savin, Andrei-Antonio; Simeonov, Vasil; Stasiulis, Ramunas; Stefanov, Georgi; Todirascu, Irinel Costel; Todorov, Stoyan; Trifonov, Preslav; Vasilev, Georgi; Vladutu, Dan-Constantin</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 12-2024.pdf</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1444,22 +1444,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2021-02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t>ADAC, Hansastr; MP, MARTIN ZAHARIEVSOZIALVERSICHER; Rundfunk ARD, ZDF; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1471,22 +1471,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; Burger King, FOOD STAR GmbH; GLOBUS SBW, CHEMNITZ; Globus SBW, Chemnitz; Gutschrift Darling züruck , Danke Mersi; MP, INH; MP, MARTIN ZAHARIEVSOZIALVERSICHER; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1498,22 +1498,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t>ADAC Versicherung AG, Hansastr; ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; Burger King, FOOD STAR GmbH; EUR, SOL; KG, Ihr Einkauf bei Parf; MP, INH; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2023 #9109.pdf</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1525,22 +1525,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t>ADAC, Hansastr; MP, MARTIN ZAHARIEVSOZIALVERSICHER; Rundfunk ARD, ZDF; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1552,22 +1552,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Arbeitsunfähigkeit, Entgeltbescheinigung bei; Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; BUONO, CHEMNITZ; GLOBUS SBW, CHEMNITZ; Gutschrift Darling züruck , Danke Mersi; MP, INH; Reece Upadhyay, Ihr Einkauf bei R; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1579,76 +1579,76 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t/>
+          <t>6</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t/>
+          <t>ADAC, Hansastr; ARD, ZDF; DANKE, IHR LIDL; MP, MARTIN ZAHARIEVSOZIALVERSICHER; Simply NetTrade GmbH, Ihr Einkauf bei Simply NetTrade Gmb; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/CarlundCarla_RG424005125.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t/>
+          <t>9</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t/>
+          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTO CENTER SUED, CHEMNITZ; BRAZIL OHG, CHEMNITZ; BUONO, CHEMNITZ; MP, INH; Reece Upadhyay, Ihr Einkauf bei R; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/CarlundCarla_RG424005157.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brunettin, Marilie</t>
+          <t>ADAC, Hansastr; ARD, ZDF; Burger King, FOOD STAR GmbH; DANKE, IHR LIDL; MP, MARTIN ZAHARIEVSOZIALVERSICHER; Simply NetTrade GmbH, Ihr Einkauf bei Simply NetTrade Gmb; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Ihre Lohnauswertungen.eml</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1660,22 +1660,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2036-08</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTO CENTER SUED, CHEMNITZ; MP, INH; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2036 08.01.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/07-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -1687,22 +1687,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2054-07</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>ADAC, Hansastr; ARD, ZDF; BRAZIL OHG, CHEMNITZ; Burger King, FOOD STAR GmbH; DANKE, IHR LIDL; MP, MARTIN ZAHARIEVSOZIALVERSICHER; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2054 07.02.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/09-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -1714,22 +1714,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2058-08</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>ADAC, Hansastr; AGIP,ANSBACHER STR; AGIP,NUERNBERG; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTO CENTER SUED, CHEMNITZ; BUONO, CHEMNITZ; Burger King, FOOD STAR GmbH; MP, INH; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2058 08.03.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/10-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -1741,103 +1741,103 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2021-08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t/>
+          <t>7</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t/>
+          <t>ADAC, Hansastr; ARD, ZDF; FAVORIT MP, MARTINSOZIALVERSICHERU; MP, MARTIN ZAHARIEVSOZIALVERSICHER; MP, MARTIN ZAHARIEVSOZIALVERSICHERU; ZAHARIEV, MARTIN ADAC VERSICHER; Überweisung Kirev,Kosta</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2765 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/11-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t/>
+          <t>11</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t/>
+          <t>ADAC, Hansastr; ARD, ZDF; Burger King, FOOD STAR GmbH; EUR, UMS; FAVORIT MP, MARTINSOZIALVERSICHERU; GLOBUS SBW, CHEMNITZ; Globus SBW, Chemnitz; MP, MARTIN ZAHARIEVSOZIALVERSICHER; MP, MARTIN ZAHARIEVSOZIALVERSICHERU; ZAHARIEV, MARTIN ADAC VERSICHER; Überweisung Kirev,Kosta</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2777 Zahariev Hermes Unterstützungstouren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t/>
+          <t>11</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t/>
+          <t>ADAC, Hansastr; AGIP,ANSBACHER STR; AGIP,NUERNBERG; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTO CENTER SUED, CHEMNITZ; BUONO, CHEMNITZ; Burger King, FOOD STAR GmbH; KG, Ihr Einkauf bei Parf; MP, INH; ZAHARIEV, MARTIN ADAC VERSICHER</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2778 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2782 Zahariev Hermes Bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2024_Brutto_Netto_00090_X0B.pdf</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -1849,7 +1849,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2788 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -1876,7 +1876,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2789 Zahariev TF Touren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/9. Nachweise zur Anmeldung der Mitarbeiter beim Sozialversicherungsträger.pdf</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -1903,61 +1903,61 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t/>
+          <t>3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t/>
+          <t>Abfindung, Entschädigung oder ähnliche Leistung wegen der Beendigung desWenn ja; Abfindung, Entschädigung oder ähnlichen Leistung zulässig; Der Arbeitgeber hätte das Arbeitsverhältnis gekündigt</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2794 Zahariev KFZ Miete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Arbeitsbescheinigung Georgi Stefanov.pdf</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
+          <t/>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2799 Bearbeitungsgebühr 10.06.2025 Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Sozialversicherungsanmeldungen 01-2020 bis 03-2021.pdf</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2810 Zahariev TF Touren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Sozialversicherungsanmeldungen.pdf</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -1984,7 +1984,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2020-06</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2811 Zahariev scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/SV-Nachweis (DEЪV)_Div Mitarbeiter_   (07-2021.pdf</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2011,76 +2011,76 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
+          <t/>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2813 zahariev bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/SV-Nachweise.pdf</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t/>
+          <t>10</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t/>
+          <t>Betreuung durch den ASD, Bescheid; EUR Warenlieferung, Forderung aus; Feuerwehr Zwickau, Kennzeichen; Ieva Meilutyte, Stefan Mihaila; Säumniszuschläge, Kosten; Säumniszuschläge, Nachzahlungszinsen und; Säumniszuschläge, Zinsen; Ventsislav Kostov, Ionel Neamtu; ZV-Sache, AG Chemnitz; Zahariev, Martin</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2814 zahariev bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157425.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Vasilev_Test Pay Slip.pdf</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2092,49 +2092,49 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t/>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t/>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157934.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/38389 - Vorgangsmappe Lohn - 38389 - Aktualisiert- Auszahlungen Inflationsprämie.xlsx</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t>Marco Brunettin; Marco Brunettin, LL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000826.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2146,22 +2146,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t/>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t>Boulevard Royal, L; Der Verkäufer behält sich vor, Verarbeitungsaufträge abzulehnen; E-Mail, Fax oder Brief; EE Amsterdam, Niederlande; Grafiken in den vom Verkäufer vorgegebenen Dateiformaten, Formatierungen; Kennedy, L; Reklamationen, Widerrufserklärungen und; Reklamationen, Widerrufserklärungen und -zusendungen oder Gutschriften; Stockholm, Schweden; Urheber-, Marken- und Persönlichkeitsrechte; Versendung, Retouren; Ware, Lieferzeit; Zahlungsabwicklung über die TeamBank AG Nürnberg, Beuthener Straße; Überweisungsgebühren, Wechselkursgebühren</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000990.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/agb_doc.pdf</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2173,34 +2173,34 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t/>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400001108-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Lohnauswertungen_August_2024.pdf</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t>Autoverwertung-Oskar, Schulstr</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400017841.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Rechnung_RE058675_11.08.2025.pdf</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2227,22 +2227,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t>Euro, Tsd; Kilometer, St; Mihaila, Stefan; Name; Petrov, Kristiyan; Tage, Km; Tausend Euro, Mio</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400018211.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Test Pay ROll.pdf</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2254,22 +2254,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t/>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t>Herleshausen, Deutschland; Post versandter Brief, Telefax oder E-Mail; Weber GmbH, Sülzbach</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035414.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/widerruf_doc.pdf</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2281,22 +2281,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dennis Kollmann, Marco Schlüter</t>
+          <t>Parfumerie Douglas GmbH, Ihr Eink auf bei Parfumeri; Parfumerie Douglas GmbH, Ihr Einkau; Skull Sh aver EU Ltd, Ihr Ei; Skull Shaver EU Ltd, Ihr Einkauf bei Skull Shaver EU Lt</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035649.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/01-2023 #9120.pdf</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2308,22 +2308,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißlog, Hohensteiner Str</t>
+          <t>ALEX Chemnitz, Galerie Roter Turm; Burger King, FOOD STAR GmbH; Limited, Ih</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Docutain Dokument.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/02-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2335,22 +2335,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t>ALEX Chemnitz, Galerie Roter Turm; AUTODOC AG, Ihr Einkau; Burger King, FOOD STAR GmbH; Dott, Ihr Einkauf bei Dott; EUR, Tra; Limited, Ih; Tier Mobility GmbH, Ihr Einkauf b</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 05.04. 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/04-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2362,22 +2362,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>ALEX Chemnitz, Galerie Roter Turm; AUTO CENTER SUED, CHEMNITZ; AUTODOC AG, Ihr Einkau; Dott, Ihr Einkauf bei Dott; Tier Mobility GmbH, Ihr Einkauf b</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 24-2024 Zahariev Martin 31.07.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/06-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2389,22 +2389,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 31-2024 Zahariev Martin 30.09.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/07-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Goetz, Schneeberg; Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t>ADAC, Hansastr; AG, Ihr Einkauf bei AUTODOC AG; ALEX Chemnitz, Galerie Roter Turm</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 34-2024 Zahariev Martin 04.10.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2443,22 +2443,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>ADAC V ersicherung AG, Hansastr; ADAC VERSICHERUNG AG, HANSASTR; ADAC, Hansastr; AGIP,ESPENHAIN; ALEX CHEMNITZ, GALERIE ROTER TURM; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTOHAUS WEINHOLD, CHEMNITZ; BURGER KING, FOOD STAR GMBH; Burger King, FOOD STAR; Burger King, FOOD STAR GmbH; FAVORIT MP, INH; MARTIN ZAH ARIEV,CHEMNITZ; Rundfunk ARD, ZDF; Rundfunk ARD,ZDF; ZAHARIEV, MARTIN ADAC VERSICHERUNG AG; ZAHLUNG, VORAUSZAHLUNG</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 38-2024 Zahariev Martin 31.10.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023.pdf</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2470,22 +2470,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>ADAC V ersicherung AG, Hansastr; ALEX Chemnitz, Galerie Roter Turm; Burger King, FOOD STAR GmbH; EUR, SOL; FAVORIT MP, INH; GLOBUS SBW, CHEMNITZ; Rundfunk ARD, ZDF; Rundfunk ARD,ZDF; Sachsen -EZU-Verfahren -, Dresden; ZAHARIEV, MARTIN ADAC VERSICHERUNG AG</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 42-2024 Zahariev Martin 30.11.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2024.pdf</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -2497,22 +2497,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>AG, Ihr Einkauf bei AUTODOC AG; EU Ltd, Ihr Einkauf bei Skull; GmbH, Ihr Einkauf bei Parfumerie Do; Parfumerie Douglas GmbH, Ihr Eink</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 44-2024 Zahariev Martin 31.12.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/12-2022 #9120.pdf</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -2524,27 +2524,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t/>
+          <t>4</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t/>
+          <t>Akkreditiert durch DAkkS, Registriernummer; Berlin-Charlottenburg, HRB; Präqualifikation Kurier-, Express- und Paketdienstleistern i; ZERTIFIZIERUNG BAU GMBH, Kronenstraße</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 66 Mai 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/20240123_60222_10160_Rechnung.pdf</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -2556,29 +2556,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t/>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 71 2025 zahariev Sendungsverlust.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1).pdf</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift April 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy10.pdf</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift märz 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy2.pdf</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -2632,7 +2632,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift Zahariev 74 30.06.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy3.pdf</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -2659,115 +2659,115 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t/>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 48 31.01.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (1)__copy4.pdf</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t/>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 51 17.02.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2) (1).pdf</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t/>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 52 28.02.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2).pdf</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t/>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 55 08.03.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2)__copy2.pdf</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2035-08</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>Sokolarski,Stanislav</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2035 08.01.2025 Hermes Bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (2)__copy3.pdf</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -2794,238 +2794,238 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2037-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t/>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2037 08.01.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (3) (1).pdf</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2038-08</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t/>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2038 08.01.2025 Bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (3).pdf</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2055-07</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t/>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2055 07.02.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (3)__copy2.pdf</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2056-07</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t/>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2056 07.02.2025 Bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform) (4).pdf</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2057-07</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t/>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2057 07.02.2025 Hermes Bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform).pdf</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2069-08</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t/>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2069 08.03.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform)__copy2.pdf</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2070-08</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2</t>
+          <t/>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t/>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2070 08.03.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform)__copy3.pdf</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t/>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t/>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2014 vom 05.12.2024 Sendungsverlust Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Abstimmliste (DE - SEPA, Langform)__copy4.pdf</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2015-07</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>Timothy Grygotis, Julia von SpechtSitz</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2015 07.12.2024 Martin Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102600491.PDF</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3037,7 +3037,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+          <t>Timothy Grygotis, Julia von SpechtSitz</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2023 vom 07.12.2024  Zahariev HERMES Bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102659867.PDF</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3064,34 +3064,34 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t/>
+          <t>1</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t/>
+          <t>Timothy Grygotis, Julia von SpechtSitz</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2764 Zahariev Hermes Kleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102665850.PDF</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+          <t>Timothy Grygotis, Julia von SpechtSitz</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2766 Zahariev Hermes Sendungsverlust.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102698674.PDF</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3118,7 +3118,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t/>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
+          <t>Andreas Weber, Horst WeberHandelsregister</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2767 Zahariev Hermes Bearbeitungsgebuhr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073-1.pdf</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -3145,22 +3145,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t/>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chemnitz , Sachs; Motoren-Frech, Uwe; Thomas Frech GbR, Hohensteiner Straße</t>
+          <t>Andreas Weber, Horst WeberHandelsregister</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/11_Contribution_Lists/RE-53380_2024 13.08.2024 09_17_16.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073.pdf</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3172,27 +3172,2970 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Timothy Grygotis, Julia von Specht</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-1.PDF</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Timothy Grygotis, Julia von Specht</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-2.PDF</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Timothy Grygotis, Julia von Specht</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980.PDF</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA - Health insurances.pdf</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA - payroll.pdf</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA - Pfändungen.pdf</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List health security-1.pdf</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List health security.pdf</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List health securitys.pdf</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List salaries (2).pdf</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List salaries.pdf</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List salaries__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List seizures.pdf</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA List seizures__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List halth security.pdf</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List health security.pdf</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Revolut Bank, Berlin</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List salaries.pdf</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Revolut Bank, Berlin</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List salaries__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Revolut Bank, Berlin</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List salaries__copy3.pdf</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List seizure.pdf</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List Seizures.pdf</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/SEPA-List seizures__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Avis Budget Autovermietung Verwaltungsgesellschaft mbH, Oberursel; KG, Amtsgericht Bad Homburg v; OBERURSEL, GERMANY; Sollten Sie Fragen, Wünsche oder auch Beanstandungen haben; Wir hoffen, Sie bald wieder bei uns begrüssen zu dürfen; ZAHARIEV,MARTIN; ZAHARIEV,MARTIN Gefahrene Entfernung</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/307538032.pdf</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/39739 - Rechnung 231128_2023 vom 28.12.2023, Aufträge 31_23, 32_23, 33_23, 34_23, 50_23, 98_23, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; EURPQ, Matodiev wage statement; Marco Brunettin; Marco Brunettin, LL; Stefanova, Yordanov</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Arbeitsunfähigkeit, Entgeltbescheinigung bei; Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
           <t>2024-09</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B155" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/CarlundCarla_RG424005125.pdf</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/CarlundCarla_RG424005157.pdf</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Brunettin, Marilie</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Ihre Lohnauswertungen.eml</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2036-08</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2036 08.01.2025 Scannermiete.pdf</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2054-07</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2054 07.02.2025 Scannermiete.pdf</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2058-08</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2058 08.03.2025 Scannermiete.pdf</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2765 Zahariev Hermes Scannermiete.pdf</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2777 Zahariev Hermes Unterstützungstouren.pdf</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2778 Zahariev Hermes Scannermiete.pdf</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2782 Zahariev Hermes Bearbeitungsgebühr.pdf</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2788 Zahariev Hermes Scannermiete.pdf</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2789 Zahariev TF Touren.pdf</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2794 Zahariev KFZ Miete.pdf</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2799 Bearbeitungsgebühr 10.06.2025 Zahariev.pdf</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2810 Zahariev TF Touren.pdf</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2811 Zahariev scannermiete.pdf</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2813 zahariev bearbeitungsgebühr.pdf</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2814 zahariev bekleidung.pdf</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157425.pdf</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157934.pdf</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000826.pdf</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000990.pdf</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400001108-1.pdf</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400017841.pdf</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400018211.pdf</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035414.pdf</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035649.pdf</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißlog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Docutain Dokument.pdf</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 05.04. 2025 zahariev.pdf</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 24-2024 Zahariev Martin 31.07.2024.pdf</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 31-2024 Zahariev Martin 30.09.2024.pdf</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Goetz, Schneeberg; Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 34-2024 Zahariev Martin 04.10.2024.pdf</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 38-2024 Zahariev Martin 31.10.2024.pdf</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 42-2024 Zahariev Martin 30.11.2024.pdf</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 44-2024 Zahariev Martin 31.12.2024.pdf</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 66 Mai 2025 zahariev.pdf</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 71 2025 zahariev Sendungsverlust.pdf</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift April 2025 zahariev.pdf</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift märz 2025 zahariev.pdf</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift Zahariev 74 30.06.2025.pdf</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 48 31.01.2025.pdf</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 51 17.02.2025.pdf</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 52 28.02.2025.pdf</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 55 08.03.2025.pdf</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2035-08</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2035 08.01.2025 Hermes Bekleidung.pdf</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2037-08</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2037 08.01.2025 Sendungsverluste.pdf</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2038-08</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2038 08.01.2025 Bearbeitungsgebühr.pdf</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2055-07</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2055 07.02.2025 Sendungsverluste.pdf</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2056-07</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2056 07.02.2025 Bearbeitungsgebühr.pdf</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2057-07</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2057 07.02.2025 Hermes Bekleidung.pdf</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2069-08</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2069 08.03.2025 Sendungsverluste.pdf</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2070-08</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2070 08.03.2025 Sendungsverluste.pdf</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2014 vom 05.12.2024 Sendungsverlust Zahariev.pdf</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2015-07</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2015 07.12.2024 Martin Zahariev.pdf</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2023 vom 07.12.2024  Zahariev HERMES Bekleidung.pdf</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2764 Zahariev Hermes Kleidung.pdf</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2766 Zahariev Hermes Sendungsverlust.pdf</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2767 Zahariev Hermes Bearbeitungsgebuhr.pdf</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
         <is>
           <t>Chemnitz , Sachs; Motoren-Frech, Uwe; Thomas Frech GbR, Hohensteiner Straße</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/11_Contribution_Lists/RE-53380_2024 13.08.2024 09_17_16.pdf</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Chemnitz , Sachs; Motoren-Frech, Uwe; Thomas Frech GbR, Hohensteiner Straße</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
         <is>
           <t>00_INBOX - Входящи - Eingang/Accounting_Organized/11_Contribution_Lists/RE-53652_2024 20.09.2024 10_56_50.pdf</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 01-2024.pdf</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 02-2024.pdf</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 03-2024.pdf</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 04-2023.pdf</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 04-2024.pdf</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 05-2023.pdf</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 06-2023.pdf</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 07-2023.pdf</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 08-2023.pdf</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 09-2023.pdf</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 10-2023.pdf</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 11-2023.pdf</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/8. Lohnabrechnungen aller Mitarbeiter.zip::8. Lohnabrechnungen aller Mitarbeiter/Entgeltabrechnungen 12-2023.pdf</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
     </row>

--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/employee_timeline.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/employee_timeline.xlsx
@@ -36,11 +36,26 @@
           <t>confidence</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>source_snippet</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>matched_pattern</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>extraction_method</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t/>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -61,13 +76,28 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Euro, Tsd; Kalev, Krasimir; Kilometer, St; Metodiev, Nikolay; Name; Tage, Km; Tanev, Martin Rangelov; Tausend Euro, Mio; Yordanov, Radi</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t/>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -88,13 +118,28 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Euro, Tsd; Kalev, Krasimir; Kilometer, St; Metodiev, Nikolay; Name; Tage, Km; Tanev, Martin Rangelov; Tausend Euro, Mio; Yordanov, Radi</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t/>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -115,13 +160,28 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dankin, Georgi; Euro, Tsd; Kilometer, St; Kostov, Ventsislav; Madzharov, Atanas Emilov; Metodiev, Nikolay; Name; Simeonov, Vasil; Stefanova, Petya; Tage, Km; Tausend Euro, Mio</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t/>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -142,13 +202,28 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dankin, Georgi; Euro, Tsd; Kilometer, St; Kostov, Ventsislav; Madzharov, Atanas Emilov; Name; Petrov, Kristiyan; Tage, Km; Tausend Euro, Mio; Todorov, Stoyan; Todorov, Vasilios</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t/>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -169,13 +244,28 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dankin, Georgi; Euro, Tsd; Kilometer, St; Kostov, Ventsislav; Madzharov, Atanas Emilov; Name; Petrov, Kristiyan; Tage, Km; Tausend Euro, Mio; Todorov, Stoyan; Todorov, Vasilios</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t/>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -196,13 +286,28 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Euro, Tsd; Kilometer, St; Mihaila, Stefan; Name; Petrov, Kristiyan; Tage, Km; Tausend Euro, Mio</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t/>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -223,13 +328,28 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Euro, Tsd; Kilometer, St; Metodiev, Nikolay; Name; Tage, Km; Tausend Euro, Mio; Todorov, Vasilios</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t/>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -250,13 +370,28 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Euro, Tsd; Kilometer, St; Madzharov, Atanas Emilov; Milcheva, Iveta; Name; Stefanova, Petya; Tage, Km; Tausend Euro, Mio</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -277,13 +412,28 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Abfindung, Entschädigung oder ähnliche Leistung wegen der Beendigung desWenn ja; Abfindung, Entschädigung oder ähnlichen Leistung zulässig; Der Arbeitgeber hätte das Arbeitsverhältnis gekündigt; Euro, Tsd; Kilometer, St; Revolut Bank, Berlin; Tage, Km; Tausend Euro, Mio</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t/>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -304,13 +454,28 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dankin, Georgi; Dimitrov, Neycho; Euro, Tsd; Kilometer, St; Name; Tage, Km; Tausend Euro, Mio</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t/>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -331,13 +496,28 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t/>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -358,13 +538,28 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t/>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -385,13 +580,28 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t/>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -412,13 +622,28 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t/>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -439,13 +664,28 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bogdan, Cosmin-Florin; Dimitrov, Neycho; Euro, Tsd; Genchev, Lyudmil; Ignat, Petronel; Kilometer, St; Name; Tage, Km; Tausend Euro, Mio; Vasilev, Georgi</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t/>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -466,13 +706,28 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t/>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -493,13 +748,28 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dimitrov, Neycho; Euro, Tsd; Kalev, Krasimir; Kilometer, St; Name; Stefanova, Petya; Tage, Km; Tanev, Martin Rangelov; Tausend Euro, Mio; Yordanov, Radi</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2018-10</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -520,6 +790,21 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ort, Datum Firmenstempel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -549,11 +834,26 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Health Security.pdf</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t/>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -574,6 +874,21 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -603,11 +918,26 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lohnauswertungen_Juli_2024.pdf</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -628,13 +958,28 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Abfindung, Entschädigung oder ähnliche Leistung wegen der Beendigung desWenn ja; Abfindung, Entschädigung oder ähnlichen Leistung zulässig; Der Arbeitgeber hätte das Arbeitsverhältnis gekündigt; Euro, Tsd; Kilometer, St; Revolut Bank, Berlin; Tage, Km; Tausend Euro, Mio</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2000-01</t>
+          <t>2020-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -655,13 +1000,28 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Abfindung, Entschädigung oder ähnliche Leistung wegen der Beendigung desWenn ja; Abfindung, Entschädigung oder ähnlichen Leistung zulässig; Arbeitslohn für mehrere Kalenderjahre, Entschädigungen z; Catana, Stefan-Andrei; Der Arbeitgeber hätte das Arbeitsverhältnis gekündigt; Dudas, Laci; Euro, Tsd; </t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t/>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -682,13 +1042,28 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -709,6 +1084,21 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Aufhebungsvertrag, AG hätte nicht oder nicht zum selben Zeitpunkt gek</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -738,6 +1128,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lohnauswertungen_Mai_2024.pdf</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -765,6 +1170,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lohnauswertungen_März_2025.pdf</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -792,6 +1212,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lohnauswertungen_November_2024-1.pdf</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -819,6 +1254,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lohnauswertungen_November_2024.pdf</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -846,6 +1296,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ignat, Petronel; Mihaylov, Bozhidar; Petrov, Kristiyan; Vasilev, Georgi</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -873,6 +1338,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Andrunachie, Ionut-Cr; Asenov, Veselin; Bimbalov, Atanas; Bogaevski, Petar N; Caciulescu, Andrei-Cosmi; Chakarov, Svetlomir; Dankin, Georgi; Dimitrov, Neycho; Dragan, Titus-Andrei; Genchev, Lyudmil; Genov, Petar N; Georgiev, Emil; Kalev, Krasimir; Kitanov, Todor; Kostov, Ventsislav; Krumov, Petar; M</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -900,6 +1380,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Revolut Bank, Berlin</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -927,6 +1422,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Seizures.pdf</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -954,6 +1464,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Zoll Kitanov.pdf</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -981,11 +1506,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Asenov, Veselin; Bimbalov, Atanas; Bogaevski, Petar; Caciulescu, Andrei-Cosmi; Chakarov, Svetlomir; Dankin, Georgi; Dimitrov, Neycho; Dragan, Titus-Andrei; Genchev, Lyudmil; Georgiev, Emil; Ivanova, Miroslava Angel; Kalev, Krasimir; Kalev, Krasimir NVJ; Kitanov, Todor; Kostov, Ventsislav; Krumov, Pe</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1006,6 +1546,21 @@
       <c r="E37" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Andrunachie, Ionut-Crist; Arbone, Alexandru-Stefan; Aufhebungsvertrag, AG hätte nicht oder nicht zum selben Zeitpunkt gek; Bogdan, Cosmin-Florin; Buricel, Nicolae-Mihai; Clanetariu, Cosmin-Ionut; Clanetariu, Vasile-Costi; Coretchi, Ion; Dobrescu, Andrei; Dragan, Titus-Andrei; Dudas, Laci; Georgiev, </t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -1035,11 +1590,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Asenov, Veselin; Bimbalov, Atanas N; Bogaevski, Petar; Caciulescu, Andrei-Cosmi; Dankin, Georgi; Dimitrov, Neycho; Dobrescu, Andrei; Dragan, Titus-Andrei; Genchev, Lyudmil; Georgiev, Emil; Ivanova, Miroslava Angel; Kalev, Krasimir; Kitanov, Todor; Koprivarov, Kiril; Kostov, Ventsislav; Krumov, Petar</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1060,6 +1630,21 @@
       <c r="E39" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Andrunachie, Ionut-Cris N; Arbone, Alexandru-Stefa N; Aufhebungsvertrag, AG hätte nicht oder nicht zum selben Zeitpunkt gek; Bogdan, Cosmin-Florin N; Boroda, Catalin; Buricel, Nicolae-Mihai N; Clanetariu, Cosmin-Ionu N; Coretchi, Ion N; Dobrescu, Andrei N; Dragan, Titus-Andrei N; Dudas, Laci N; Geor</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -1089,11 +1674,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Asenov, Veselin; Bogaevski, Petar; Dankin, Georgi; Dimitrov, Neycho; Dobrescu, Andrei; Dragan, Titus-Andrei; Genchev, Lyudmil; Georgiev, Emil; Grigorescu, Stefan-Vasil; Ivanova, Miroslava Angel; Kitanov, Todor; Koprivarov, Kiril; Kostov, Ventsislav; Krumov, Petar; Lacatusu, Marius-Iulian; Madzharov,</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1114,6 +1714,21 @@
       <c r="E41" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Andrunachie, Ionut-Crist; Arbone, Alexandru-Stefan; Aufhebungsvertrag, AG hätte nicht oder nicht zum selben Zeitpunkt gek; Bogdan, Cosmin-Florin; Boroda, Catalin; Clanetariu, Cosmin-Ionut; Coretchi, Ion; Dobrescu, Andrei N; Dragan, Titus-Andrei; Dudas, Laci; Feraru, Andrei; Georgiev, Emil; Kitanov, </t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -1143,11 +1758,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Bogaevski, Petar; Dankin, Georgi; Dimitrov, Neycho N; Dobrescu, Andrei; Dragan, Titus-Andrei; Genchev, Lyudmil; Georgiev, Emil; Grigorescu, Stefan-Vasil; Ivanova, Miroslava Angel; Kitanov, Todor; Kostov, Ventsislav; Krumov, Petar; Lacatusu, Marius-Iulian; Madzharov, Atanas Emilov; Metodiev, Nikolay;</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2020-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1168,6 +1798,21 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Abfindung, Entschädigung oder ähnliche Leistung wegen der Beendigung desWenn ja; Abfindung, Entschädigung oder ähnlichen Leistung zulässig; Andrunachie, Ionut-Crist; Arbeitslohn für mehrere Kalenderjahre, Entschädigungen z; Arbone, Alexandru-Stef; Catana, Stefan-Andrei; Clanetariu, Cosmin-Ion; Coret</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -1197,11 +1842,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Bogaevski, Petar; Dankin, Georgi; Dimitrov, Neycho; Dobrescu, Andrei; Dragan, Titus-Andrei; Genchev, Lyudmil; Georgiev, Emil; Grigorescu, Stefan-Vasil; Kitanov, Todor; Kostov, Ventsislav; Kostova, Sofia; Krumov, Petar; Lacatusu, Marius-Iulian; Madzharov, Atanas Emilov; Metodiev, Nikolay; Mihaila, St</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2001-03</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1222,6 +1882,21 @@
       <c r="E45" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Andrunachie, Ionut-Crist; Arbeitslohn für mehrere Kalenderjahre, Entschädigungen z; Catana, Stefan-Andrei; Coretchi, Ion; Dragan, Titus-Andrei; Dudas, Laci; Euro, Tsd; Feraru, Andrei; Georgiev, Emil; Jaleru, Marius-Gabriel; Kilometer, St; Kitanov, Todor; Kostova, Sofia; Lupascu, Florin-Madal; Madzha</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -1251,11 +1926,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bogaevski, Petar; Dankin, Georgi; Dimitrov, Neycho; Dobrescu, Andrei; Dragan, Titus-Andrei; Genchev, Lyudmil; Georgiev, Emil; Grigorescu, Stefan-Vasil; Ignat, Petronel; Kitanov, Todor; Kostov, Ventsislav; Kostova, Sofia; Krumov, Petar; Madzharov, Atanas Emilo N; Madzharov, Atanas Emilov; Metodiev, N</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2000-01</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1276,6 +1966,21 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Abfindung, Entschädigung oder ähnliche Leistung wegen der Beendigung desWenn ja; Abfindung, Entschädigung oder ähnlichen Leistung zulässig; Andrunachie, Ionut-Crist; Arbeitslohn für mehrere Kalenderjahre, Entschädigungen z; Aufhebungsvertrag, AG hätte nicht oder nicht zum selben Zeitpunkt gek; Catan</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -1305,6 +2010,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bogaevski, Petar; Dankin, Georgi; Dimitrov, Neycho; Dobrescu, Andrei; Dragan, Titus-Andrei; Dudas, Laci; Genchev, Lyudmil; Georgiev, Emil; Grigorescu, Stefan-Vasil; Ignat, Petronel; Kitanov, Todor; Kostov, Ventsislav; Kostova, Sofia; Krumov, Petar; Metodiev, Nikolay; Mihaila, Stefan; Mihaylov, Bozhi</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1332,11 +2052,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Andrunachie, Ionut-Crist; Bogaevski, Petar; Bogdan, Cosmin-Florin; Dankin, Georgi; Dimitrov, Neycho; Divile, Ciprian; Dobrescu, Andrei; Dragan, Titus-Andrei; Dudas, Laci; Dunaroae, Dumitru-Marian; Genchev, Lyudmil; Georgiev, Emil; Grigorescu, Stefan-Vasil; Ignat, Petronel; Kitanov, Todor; Kostov, Ve</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1357,6 +2092,21 @@
       <c r="E50" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Andrunachie, Ionut-Cris N; Arbone, Alexandru-Stefan; Bogdan, Cosmin-Florin; Buricel, Nicolae-Mihai; Clanetariu, Cosmin-Ionut; Clanetariu, Vasile-Costi; Coretchi, Ion; Dankin, Georgi; Dimitrov, Neycho; Divile, Ciprian; Dobrescu, Andrei; Dragan, Titus-Andrei; Dudas, Laci; Dunaroae, Dumitru-Marian; Gen</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -1386,6 +2136,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Andrunachie, Ionut-Crist; Arbone, Alexandru-Stefan; Bogdan, Cosmin-Florin; Buricel, Nicolae-Mihai; Clanetariu, Cosmin-Ionut; Clanetariu, Vasile-Costi; Coretchi, Ion; Dimitrov, Neycho; Dobrescu, Andrei; Dragan, Titus-Andrei N; Dudas, Laci; Dunaroae, Dumitru-Marian; Georgiev, Emil; Grigorescu, Stefan-</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1413,11 +2178,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Andrunachie, Ionut-Crist; Arbone, Alexandru-Stefan; Bogdan, Cosmin-Florin; Buricel, Nicolae-Mihai; Clanetariu, Cosmin-Ionut; Clanetariu, Vasile-Costi; Coretchi, Ion; Dimitrov, Neycho N; Dobrescu, Andrei N; Dragan, Titus-Andrei; Dudas, Laci; Dunaroae, Dumitru-Mar; Georgiev, Emil; Grigorescu, Stefan-V</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1438,6 +2218,21 @@
       <c r="E53" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Andrunachie, Ionut-Crist; Andrunachie, Ionut-Cristian; Arbone, Alexandru-Stefan; Aufhebungsvertrag, AG hätte nicht oder nicht zum selben Zeitpunkt gek; Bogdan, Cosmin-Florin; Buricel, Nicolae-Mihai; Clanetariu, Cosmin-Ionut; Clanetariu, Vasile-Costi; Clanetariu, Vasile-Costinel; Coretchi, Ion; Dobre</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -1467,11 +2262,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ADAC, Hansastr; MP, MARTIN ZAHARIEVSOZIALVERSICHER; Rundfunk ARD, ZDF; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2022-02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1492,13 +2302,28 @@
       <c r="E55" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; Burger King, FOOD STAR GmbH; GLOBUS SBW, CHEMNITZ; Globus SBW, Chemnitz; Gutschrift Darling züruck , Danke Mersi; MP, INH; MP, MARTIN ZAHARIEVSOZIALVERSICHER; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2023-03</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1519,6 +2344,21 @@
       <c r="E56" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>ADAC Versicherung AG, Hansastr; ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; Burger King, FOOD STAR GmbH; EUR, SOL; KG, Ihr Einkauf bei Parf; MP, INH; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -1548,11 +2388,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ADAC, Hansastr; MP, MARTIN ZAHARIEVSOZIALVERSICHER; Rundfunk ARD, ZDF; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2022-05</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1573,6 +2428,21 @@
       <c r="E58" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; BUONO, CHEMNITZ; GLOBUS SBW, CHEMNITZ; Gutschrift Darling züruck , Danke Mersi; MP, INH; Reece Upadhyay, Ihr Einkauf bei R; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -1602,11 +2472,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ADAC, Hansastr; ARD, ZDF; DANKE, IHR LIDL; MP, MARTIN ZAHARIEVSOZIALVERSICHER; Simply NetTrade GmbH, Ihr Einkauf bei Simply NetTrade Gmb; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2022-07</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1627,6 +2512,21 @@
       <c r="E60" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTO CENTER SUED, CHEMNITZ; BRAZIL OHG, CHEMNITZ; BUONO, CHEMNITZ; MP, INH; Reece Upadhyay, Ihr Einkauf bei R; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -1656,11 +2556,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ADAC, Hansastr; ARD, ZDF; Burger King, FOOD STAR GmbH; DANKE, IHR LIDL; MP, MARTIN ZAHARIEVSOZIALVERSICHER; Simply NetTrade GmbH, Ihr Einkauf bei Simply NetTrade Gmb; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1681,13 +2596,28 @@
       <c r="E62" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTO CENTER SUED, CHEMNITZ; MP, INH; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2021-09</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1708,6 +2638,21 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>ADAC, Hansastr; ARD, ZDF; BRAZIL OHG, CHEMNITZ; Burger King, FOOD STAR GmbH; DANKE, IHR LIDL; MP, MARTIN ZAHARIEVSOZIALVERSICHER; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -1737,11 +2682,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ADAC, Hansastr; AGIP,ANSBACHER STR; AGIP,NUERNBERG; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTO CENTER SUED, CHEMNITZ; BUONO, CHEMNITZ; Burger King, FOOD STAR GmbH; MP, INH; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2021-11</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1762,6 +2722,21 @@
       <c r="E65" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ADAC, Hansastr; ARD, ZDF; FAVORIT MP, MARTINSOZIALVERSICHERU; MP, MARTIN ZAHARIEVSOZIALVERSICHER; MP, MARTIN ZAHARIEVSOZIALVERSICHERU; ZAHARIEV, MARTIN ADAC VERSICHER; Überweisung Kirev,Kosta</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -1791,6 +2766,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ADAC, Hansastr; ARD, ZDF; Burger King, FOOD STAR GmbH; EUR, UMS; FAVORIT MP, MARTINSOZIALVERSICHERU; GLOBUS SBW, CHEMNITZ; Globus SBW, Chemnitz; MP, MARTIN ZAHARIEVSOZIALVERSICHER; MP, MARTIN ZAHARIEVSOZIALVERSICHERU; ZAHARIEV, MARTIN ADAC VERSICHER; Überweisung Kirev,Kosta</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1818,11 +2808,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ADAC, Hansastr; AGIP,ANSBACHER STR; AGIP,NUERNBERG; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTO CENTER SUED, CHEMNITZ; BUONO, CHEMNITZ; Burger King, FOOD STAR GmbH; KG, Ihr Einkauf bei Parf; MP, INH; ZAHARIEV, MARTIN ADAC VERSICHER</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t/>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1843,6 +2848,21 @@
       <c r="E68" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -1872,6 +2892,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>38389 - Vorgangsmappe Lohn - Contributions 28.05.2025.docx</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1899,11 +2934,26 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>9. Nachweise zur Anmeldung der Mitarbeiter beim Sozialversicherungsträger.pdf</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1924,13 +2974,28 @@
       <c r="E71" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Abfindung, Entschädigung oder ähnliche Leistung wegen der Beendigung desWenn ja; Abfindung, Entschädigung oder ähnlichen Leistung zulässig; Der Arbeitgeber hätte das Arbeitsverhältnis gekündigt</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2020-01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1951,13 +3016,28 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Sozialversicherungsanmeldungen 01-2020 bis 03-2021.pdf</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2022-04</t>
+          <t/>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1978,13 +3058,28 @@
       <c r="E73" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Sozialversicherungsanmeldungen.pdf</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2020-06</t>
+          <t>2021-07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2005,6 +3100,21 @@
       <c r="E74" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>SV-Nachweis (DEЪV)_Div Mitarbeiter_ (07-2021.pdf</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -2034,11 +3144,26 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>SV-Nachweise.pdf</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2059,13 +3184,28 @@
       <c r="E76" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Betreuung durch den ASD, Bescheid; EUR Warenlieferung, Forderung aus; Feuerwehr Zwickau, Kennzeichen; Ieva Meilutyte, Stefan Mihaila; Säumniszuschläge, Kosten; Säumniszuschläge, Nachzahlungszinsen und; Säumniszuschläge, Zinsen; Ventsislav Kostov, Ionel Neamtu; ZV-Sache, AG Chemnitz; Zahariev, Martin</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t/>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2086,6 +3226,21 @@
       <c r="E77" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Euro, Tsd; Kilometer, St; Tage, Km; Tausend Euro, Mio</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -2115,6 +3270,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>38389 - Vorgangsmappe Lohn - 38389 - Aktualisiert- Auszahlungen Inflationsprämie.xlsx</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2142,6 +3312,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2169,6 +3354,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Boulevard Royal, L; Der Verkäufer behält sich vor, Verarbeitungsaufträge abzulehnen; E-Mail, Fax oder Brief; EE Amsterdam, Niederlande; Grafiken in den vom Verkäufer vorgegebenen Dateiformaten, Formatierungen; Kennedy, L; Reklamationen, Widerrufserklärungen und; Reklamationen, Widerrufserklärungen u</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2196,11 +3396,26 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Lohnauswertungen_August_2024.pdf</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2221,13 +3436,28 @@
       <c r="E82" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Autoverwertung-Oskar, Schulstr</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t/>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2248,6 +3478,21 @@
       <c r="E83" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Euro, Tsd; Kilometer, St; Mihaila, Stefan; Name; Petrov, Kristiyan; Tage, Km; Tausend Euro, Mio</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -2277,11 +3522,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Herleshausen, Deutschland; Post versandter Brief, Telefax oder E-Mail; Weber GmbH, Sülzbach</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2022-11</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2302,6 +3562,21 @@
       <c r="E85" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Parfumerie Douglas GmbH, Ihr Eink auf bei Parfumeri; Parfumerie Douglas GmbH, Ihr Einkau; Skull Sh aver EU Ltd, Ihr Ei; Skull Shaver EU Ltd, Ihr Einkauf bei Skull Shaver EU Lt</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -2331,6 +3606,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ALEX Chemnitz, Galerie Roter Turm; Burger King, FOOD STAR GmbH; Limited, Ih</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2358,6 +3648,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>ALEX Chemnitz, Galerie Roter Turm; AUTODOC AG, Ihr Einkau; Burger King, FOOD STAR GmbH; Dott, Ihr Einkauf bei Dott; EUR, Tra; Limited, Ih; Tier Mobility GmbH, Ihr Einkauf b</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2385,11 +3690,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ALEX Chemnitz, Galerie Roter Turm; AUTO CENTER SUED, CHEMNITZ; AUTODOC AG, Ihr Einkau; Dott, Ihr Einkauf bei Dott; Tier Mobility GmbH, Ihr Einkauf b</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2022-08</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2410,6 +3730,21 @@
       <c r="E89" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>ADAC, Hansastr; ALEX Chemnitz, Galerie Roter Turm</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -2439,11 +3774,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>ADAC, Hansastr; AG, Ihr Einkauf bei AUTODOC AG; ALEX Chemnitz, Galerie Roter Turm</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2464,13 +3814,28 @@
       <c r="E91" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>ADAC V ersicherung AG, Hansastr; ADAC VERSICHERUNG AG, HANSASTR; ADAC, Hansastr; AGIP,ESPENHAIN; ALEX CHEMNITZ, GALERIE ROTER TURM; ALEX Chemnitz, Galerie Roter Turm; ARD, ZDF; AUTOHAUS WEINHOLD, CHEMNITZ; BURGER KING, FOOD STAR GMBH; Burger King, FOOD STAR; Burger King, FOOD STAR GmbH; FAVORIT MP, </t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2491,6 +3856,21 @@
       <c r="E92" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>ADAC V ersicherung AG, Hansastr; ALEX Chemnitz, Galerie Roter Turm; Burger King, FOOD STAR GmbH; EUR, SOL; FAVORIT MP, INH; GLOBUS SBW, CHEMNITZ; Rundfunk ARD, ZDF; Rundfunk ARD,ZDF; Sachsen -EZU-Verfahren -, Dresden; ZAHARIEV, MARTIN ADAC VERSICHERUNG AG</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -2520,11 +3900,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>AG, Ihr Einkauf bei AUTODOC AG; EU Ltd, Ihr Einkauf bei Skull; GmbH, Ihr Einkauf bei Parfumerie Do; Parfumerie Douglas GmbH, Ihr Eink</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2545,6 +3940,21 @@
       <c r="E94" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Akkreditiert durch DAkkS, Registriernummer; Berlin-Charlottenburg, HRB; Präqualifikation Kurier-, Express- und Paketdienstleistern i; ZERTIFIZIERUNG BAU GMBH, Kronenstraße</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -2574,6 +3984,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Abstimmliste (DE - SEPA, Langform) (1).pdf</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2601,6 +4026,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Abstimmliste (DE - SEPA, Langform) (1)__copy10.pdf</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2628,6 +4068,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Abstimmliste (DE - SEPA, Langform) (1)__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2655,6 +4110,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Abstimmliste (DE - SEPA, Langform) (1)__copy3.pdf</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2682,6 +4152,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Abstimmliste (DE - SEPA, Langform) (1)__copy4.pdf</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2709,6 +4194,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Abstimmliste (DE - SEPA, Langform) (2) (1).pdf</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2736,6 +4236,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Abstimmliste (DE - SEPA, Langform) (2).pdf</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2763,6 +4278,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Abstimmliste (DE - SEPA, Langform) (2)__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2790,6 +4320,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Sokolarski,Stanislav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2817,6 +4362,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Abstimmliste (DE - SEPA, Langform) (3) (1).pdf</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2844,6 +4404,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Abstimmliste (DE - SEPA, Langform) (3).pdf</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2871,6 +4446,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Abstimmliste (DE - SEPA, Langform) (3)__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2898,6 +4488,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Abstimmliste (DE - SEPA, Langform) (4).pdf</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2925,6 +4530,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Abstimmliste (DE - SEPA, Langform).pdf</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2952,6 +4572,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Abstimmliste (DE - SEPA, Langform)__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2979,6 +4614,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Abstimmliste (DE - SEPA, Langform)__copy3.pdf</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3006,6 +4656,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Abstimmliste (DE - SEPA, Langform)__copy4.pdf</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3033,6 +4698,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Timothy Grygotis, Julia von SpechtSitz</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3060,6 +4740,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Timothy Grygotis, Julia von SpechtSitz</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3087,6 +4782,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Timothy Grygotis, Julia von SpechtSitz</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3114,11 +4824,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Timothy Grygotis, Julia von SpechtSitz</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3139,13 +4864,28 @@
       <c r="E116" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Andreas Weber, Horst WeberHandelsregister</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3166,6 +4906,21 @@
       <c r="E117" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Andreas Weber, Horst WeberHandelsregister</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -3195,6 +4950,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Timothy Grygotis, Julia von Specht</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3222,6 +4992,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Timothy Grygotis, Julia von Specht</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3249,6 +5034,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Timothy Grygotis, Julia von Specht</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3276,6 +5076,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>SEPA - Health insurances.pdf</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3303,6 +5118,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>SEPA - payroll.pdf</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3330,6 +5160,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>SEPA - Pfändungen.pdf</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3357,6 +5202,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>SEPA List health security-1.pdf</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3384,6 +5244,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>SEPA List health security.pdf</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3411,6 +5286,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>SEPA List health securitys.pdf</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3438,6 +5328,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>SEPA List salaries (2).pdf</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3465,6 +5370,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>SEPA List salaries.pdf</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3492,6 +5412,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>SEPA List salaries__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3519,6 +5454,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>SEPA List seizures.pdf</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3546,6 +5496,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>SEPA List seizures__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3573,6 +5538,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>SEPA-List halth security.pdf</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3600,6 +5580,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>SEPA-List health security.pdf</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3627,6 +5622,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Revolut Bank, Berlin</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3654,6 +5664,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Revolut Bank, Berlin</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3681,6 +5706,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Revolut Bank, Berlin</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3708,6 +5748,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>SEPA-List seizure.pdf</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3735,6 +5790,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>SEPA-List Seizures.pdf</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3762,11 +5832,26 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>SEPA-List seizures__copy2.pdf</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t/>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3787,6 +5872,21 @@
       <c r="E140" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Avis Budget Autovermietung Verwaltungsgesellschaft mbH, Oberursel; KG, Amtsgericht Bad Homburg v; OBERURSEL, GERMANY; Sollten Sie Fragen, Wünsche oder auch Beanstandungen haben; Wir hoffen, Sie bald wieder bei uns begrüssen zu dürfen; ZAHARIEV,MARTIN; ZAHARIEV,MARTIN Gefahrene Entfernung</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -3816,6 +5916,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3843,6 +5958,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3870,6 +6000,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3897,6 +6042,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3924,6 +6084,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3951,6 +6126,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3978,6 +6168,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4005,6 +6210,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; EURPQ, Matodiev wage statement; Marco Brunettin; Marco Brunettin, LL; Stefanova, Yordanov</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4032,6 +6252,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4059,6 +6294,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4086,6 +6336,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4113,6 +6378,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4140,6 +6420,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4167,6 +6462,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Arbeitsunfähigkeit, Entgeltbescheinigung bei; Brunettin, Mari; Marco Brunettin; Marco Brunettin, LL</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4194,6 +6504,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>CarlundCarla_RG424005125.pdf</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4221,6 +6546,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>CarlundCarla_RG424005157.pdf</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4248,11 +6588,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Brunettin, Marilie</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2036-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4273,13 +6628,28 @@
       <c r="E158" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2054-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4300,13 +6670,28 @@
       <c r="E159" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2058-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4327,13 +6712,28 @@
       <c r="E160" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t/>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4354,13 +6754,28 @@
       <c r="E161" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Rechnung 2765 Zahariev Hermes Scannermiete.pdf</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t/>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4381,13 +6796,28 @@
       <c r="E162" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Rechnung 2777 Zahariev Hermes Unterstützungstouren.pdf</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t/>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4408,6 +6838,21 @@
       <c r="E163" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Rechnung 2778 Zahariev Hermes Scannermiete.pdf</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -4437,11 +6882,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t/>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4462,13 +6922,28 @@
       <c r="E165" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Rechnung 2788 Zahariev Hermes Scannermiete.pdf</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t/>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4489,13 +6964,28 @@
       <c r="E166" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Rechnung 2789 Zahariev TF Touren.pdf</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t/>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4516,6 +7006,21 @@
       <c r="E167" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Rechnung 2794 Zahariev KFZ Miete.pdf</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -4545,11 +7050,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t/>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4570,13 +7090,28 @@
       <c r="E169" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Rechnung 2810 Zahariev TF Touren.pdf</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t/>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4597,6 +7132,21 @@
       <c r="E170" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Rechnung 2811 Zahariev scannermiete.pdf</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -4626,11 +7176,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t/>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4651,6 +7216,21 @@
       <c r="E172" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Rechnung 2814 zahariev bekleidung.pdf</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -4680,6 +7260,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4707,6 +7302,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4734,6 +7344,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4761,6 +7386,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4788,6 +7428,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4815,6 +7470,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4842,6 +7512,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4869,6 +7554,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4896,11 +7596,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Dennis Kollmann, Marco Schlüter</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4921,13 +7636,28 @@
       <c r="E182" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißlog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4948,6 +7678,21 @@
       <c r="E183" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -4977,6 +7722,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5004,11 +7764,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5029,6 +7804,21 @@
       <c r="E186" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Goetz, Schneeberg; Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -5058,6 +7848,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5085,6 +7890,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5112,6 +7932,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5139,11 +7974,26 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>gutschrift 66 Mai 2025 zahariev.pdf</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5164,6 +8014,21 @@
       <c r="E191" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -5193,6 +8058,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>gutschrift April 2025 zahariev.pdf</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5220,6 +8100,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>gutschrift märz 2025 zahariev.pdf</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5247,6 +8142,21 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Gutschrift Zahariev 74 30.06.2025.pdf</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5274,11 +8184,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5299,6 +8224,21 @@
       <c r="E196" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -5328,11 +8268,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5353,13 +8308,28 @@
       <c r="E198" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2035-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5380,13 +8350,28 @@
       <c r="E199" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2037-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5407,13 +8392,28 @@
       <c r="E200" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2038-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5434,13 +8434,28 @@
       <c r="E201" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2055-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5461,13 +8476,28 @@
       <c r="E202" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2056-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5488,13 +8518,28 @@
       <c r="E203" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2057-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5515,13 +8560,28 @@
       <c r="E204" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2069-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5542,13 +8602,28 @@
       <c r="E205" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str; Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2070-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5569,6 +8644,21 @@
       <c r="E206" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -5598,11 +8688,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2015-07</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5623,6 +8728,21 @@
       <c r="E208" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung; Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -5652,11 +8772,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Logistikbetrieb Weißflog, Hohensteiner Str</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t/>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5677,13 +8812,28 @@
       <c r="E210" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Rechnung 2764 Zahariev Hermes Kleidung.pdf</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t/>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5704,6 +8854,21 @@
       <c r="E211" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Steuerbereinigter Schadenersatz, Schadenbetrag ohne Mehrwertsteuer</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
@@ -5733,6 +8898,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Bearbeitungsgebühr, Prüfung und Erstellung</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5760,6 +8940,21 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Chemnitz , Sachs; Motoren-Frech, Uwe; Thomas Frech GbR, Hohensteiner Straße</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5787,11 +8982,26 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Chemnitz , Sachs; Motoren-Frech, Uwe; Thomas Frech GbR, Hohensteiner Straße</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5812,13 +9022,28 @@
       <c r="E215" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Entgeltabrechnungen 01-2024.pdf</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5839,13 +9064,28 @@
       <c r="E216" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Entgeltabrechnungen 02-2024.pdf</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5866,13 +9106,28 @@
       <c r="E217" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Entgeltabrechnungen 03-2024.pdf</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2023-04</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5893,13 +9148,28 @@
       <c r="E218" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Entgeltabrechnungen 04-2023.pdf</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5920,13 +9190,28 @@
       <c r="E219" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Entgeltabrechnungen 04-2024.pdf</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2023-05</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5947,13 +9232,28 @@
       <c r="E220" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Entgeltabrechnungen 05-2023.pdf</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2023-06</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5974,13 +9274,28 @@
       <c r="E221" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Entgeltabrechnungen 06-2023.pdf</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6001,13 +9316,28 @@
       <c r="E222" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Entgeltabrechnungen 07-2023.pdf</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6028,13 +9358,28 @@
       <c r="E223" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Entgeltabrechnungen 08-2023.pdf</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6055,13 +9400,28 @@
       <c r="E224" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Entgeltabrechnungen 09-2023.pdf</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6082,13 +9442,28 @@
       <c r="E225" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Entgeltabrechnungen 10-2023.pdf</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2023-11</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6109,13 +9484,28 @@
       <c r="E226" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Entgeltabrechnungen 11-2023.pdf</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6136,6 +9526,21 @@
       <c r="E227" t="inlineStr">
         <is>
           <t>LOW</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Entgeltabrechnungen 12-2023.pdf</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>employee name pattern</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>employee_timeline</t>
         </is>
       </c>
     </row>
